--- a/جر د شهر 8.xlsx
+++ b/جر د شهر 8.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\جرد شهر 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D3EFD6-540F-48AA-9B1B-1F736B67DC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{031788DC-5BC8-CF41-AF19-40EAABFD6849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14040" xr2:uid="{86282878-4084-4E7F-B814-2BEB8919EF4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" xr2:uid="{86282878-4084-4E7F-B814-2BEB8919EF4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$H$375</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$H$374</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,6 +30,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="252">
   <si>
     <t>اكياس برجر الهنا ص</t>
   </si>
@@ -757,9 +759,6 @@
   </si>
   <si>
     <t xml:space="preserve">شرش بودر </t>
-  </si>
-  <si>
-    <t>أكياس استربس ص SP</t>
   </si>
   <si>
     <t>أكياس بانيه الهنا 5 ك</t>
@@ -802,11 +801,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -814,7 +813,7 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -825,13 +824,146 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="23"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="60"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="63"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color indexed="56"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -855,8 +987,113 @@
         <fgColor indexed="11"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="27"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="29"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="36"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="49"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="62"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1025,11 +1262,159 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="63"/>
+      </left>
+      <right style="double">
+        <color indexed="63"/>
+      </right>
+      <top style="double">
+        <color indexed="63"/>
+      </top>
+      <bottom style="double">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="62"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="30"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="52"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="62"/>
+      </top>
+      <bottom style="double">
+        <color indexed="62"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1059,10 +1444,51 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="44">
+    <cellStyle name="20% - Accent1" xfId="3" xr:uid="{98BF7EF2-0FB0-4F53-BF07-4F0204879330}"/>
+    <cellStyle name="20% - Accent2" xfId="4" xr:uid="{61FCF3CC-69D1-4D95-8826-05F1208358EF}"/>
+    <cellStyle name="20% - Accent3" xfId="5" xr:uid="{507B8746-5290-4963-9502-CAA611642737}"/>
+    <cellStyle name="20% - Accent4" xfId="6" xr:uid="{4B61ABEE-4455-4943-93AC-61552CC0C3E4}"/>
+    <cellStyle name="20% - Accent5" xfId="7" xr:uid="{E760FA76-6D12-44E0-9026-1A2A0A55ECFF}"/>
+    <cellStyle name="20% - Accent6" xfId="8" xr:uid="{835FBC51-BAC5-4D3F-9BF8-8B4FC146F677}"/>
+    <cellStyle name="40% - Accent1" xfId="9" xr:uid="{49F90F62-4207-4E6D-858E-B7B8920769A4}"/>
+    <cellStyle name="40% - Accent2" xfId="10" xr:uid="{6AE962DF-0A0D-4E32-834F-32D19360757F}"/>
+    <cellStyle name="40% - Accent3" xfId="11" xr:uid="{EB077589-326C-4917-B1E2-2896A8A2D79C}"/>
     <cellStyle name="40% - Accent3 2" xfId="2" xr:uid="{6FD4C5EA-656B-4A54-9048-8C03FFF91696}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="40% - Accent4" xfId="12" xr:uid="{8F1998A5-49AF-45A1-BF97-96EE3842AC83}"/>
+    <cellStyle name="40% - Accent5" xfId="13" xr:uid="{C2106FA8-F990-4671-A7A5-0F7673513D5A}"/>
+    <cellStyle name="40% - Accent6" xfId="14" xr:uid="{5EACC164-F7BB-42BA-A2BB-77E569060AD6}"/>
+    <cellStyle name="60% - Accent1" xfId="15" xr:uid="{A5FF2B1C-8CD5-4C68-8C72-77151C5C7046}"/>
+    <cellStyle name="60% - Accent2" xfId="16" xr:uid="{E934D724-9A35-4734-B5AB-15307F7F57B7}"/>
+    <cellStyle name="60% - Accent3" xfId="17" xr:uid="{B8744FB7-0A5F-483B-90F9-F16C6BF6576B}"/>
+    <cellStyle name="60% - Accent4" xfId="18" xr:uid="{D4ABCFFB-34CE-4AEA-9214-8DC1F1F82390}"/>
+    <cellStyle name="60% - Accent5" xfId="19" xr:uid="{B0B40576-1712-4E5D-ADC6-4D6517B519F5}"/>
+    <cellStyle name="60% - Accent6" xfId="20" xr:uid="{1F0E09F3-C85A-487F-B414-A7F2619BCE0A}"/>
+    <cellStyle name="Accent1" xfId="21" xr:uid="{51916046-9288-4605-83B1-F9439383DBFF}"/>
+    <cellStyle name="Accent2" xfId="22" xr:uid="{1BEFA8AC-68D2-4860-90C8-28604CE76EE1}"/>
+    <cellStyle name="Accent3" xfId="23" xr:uid="{FA6B71EF-CF1A-4515-938B-C05B91BB3E1B}"/>
+    <cellStyle name="Accent4" xfId="24" xr:uid="{F390CE8B-2702-4AD5-B30B-6604388BB80A}"/>
+    <cellStyle name="Accent5" xfId="25" xr:uid="{DDBA87CC-EB90-4908-A4CF-BD900FCD94AF}"/>
+    <cellStyle name="Accent6" xfId="26" xr:uid="{58AE080C-AB09-4396-B9F4-23891BEFF670}"/>
+    <cellStyle name="Bad" xfId="27" xr:uid="{C30D80BA-847D-4CBB-9960-64BE342AEE0B}"/>
+    <cellStyle name="Calculation" xfId="28" xr:uid="{92190C74-EA60-4384-A5B1-9C3AEA66B581}"/>
+    <cellStyle name="Check Cell" xfId="29" xr:uid="{ACD2E0A9-EEC8-46F1-A764-A832E8205C0C}"/>
+    <cellStyle name="Explanatory Text" xfId="30" xr:uid="{95AAD415-486B-4D03-8679-DD6EFD0E79AF}"/>
+    <cellStyle name="Good" xfId="31" xr:uid="{C6F96AA7-3CBF-4F5C-B87F-BAA6F9BD6F2E}"/>
+    <cellStyle name="Heading 1" xfId="32" xr:uid="{7DA58484-70E6-43CA-9FF6-582BA163965F}"/>
+    <cellStyle name="Heading 2" xfId="33" xr:uid="{3713F434-0C62-44F1-894E-3529126351B6}"/>
+    <cellStyle name="Heading 3" xfId="34" xr:uid="{41F8E502-442E-4D07-80A9-F4A03C9BDC83}"/>
+    <cellStyle name="Heading 4" xfId="35" xr:uid="{F3C33703-63F0-4CAB-9769-5D607BDD9ECA}"/>
+    <cellStyle name="Input" xfId="36" xr:uid="{7D6B1DE4-9F12-431F-B0AD-CA692504543A}"/>
+    <cellStyle name="Linked Cell" xfId="37" xr:uid="{899D87CD-D0C0-4671-A687-C4D69228AFBE}"/>
+    <cellStyle name="Neutral" xfId="38" xr:uid="{CF81082A-0AF5-4439-9D96-8EF23E785E9D}"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CAB98B09-382F-4261-9B16-A82BDD194821}"/>
+    <cellStyle name="Note" xfId="39" xr:uid="{3157DEA9-BBDD-4235-9699-7909B97D4450}"/>
+    <cellStyle name="Output" xfId="40" xr:uid="{2E617861-6889-40D6-84DC-6738D9D08BFB}"/>
+    <cellStyle name="Title" xfId="41" xr:uid="{C437FD37-8E5D-41DF-A214-EADD331C7B5C}"/>
+    <cellStyle name="Total" xfId="42" xr:uid="{4D135EE2-9599-4AAC-B6BE-E010B175EC70}"/>
+    <cellStyle name="Warning Text" xfId="43" xr:uid="{D584DC6B-40E5-4D4E-8F13-B212D7A0A206}"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1078,9 +1504,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - نسق 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1118,7 +1544,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1224,7 +1650,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1366,7 +1792,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1374,29 +1800,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69590074-F9E1-47CB-9D65-9D1D53B05140}">
-  <dimension ref="A2:I153"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:I152"/>
+  <sheetFormatPr defaultColWidth="9.19140625" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.94921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.30859375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.19140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="D2" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="18.75" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>74</v>
       </c>
@@ -1425,7 +1851,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>79</v>
       </c>
@@ -1453,7 +1879,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>80</v>
       </c>
@@ -1483,7 +1909,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>81</v>
       </c>
@@ -1511,7 +1937,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>82</v>
       </c>
@@ -1541,7 +1967,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>83</v>
       </c>
@@ -1569,7 +1995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>84</v>
       </c>
@@ -1599,7 +2025,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>85</v>
       </c>
@@ -1627,7 +2053,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>86</v>
       </c>
@@ -1655,7 +2081,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>87</v>
       </c>
@@ -1685,7 +2111,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>88</v>
       </c>
@@ -1715,7 +2141,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>89</v>
       </c>
@@ -1745,7 +2171,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>90</v>
       </c>
@@ -1775,7 +2201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>91</v>
       </c>
@@ -1805,7 +2231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>92</v>
       </c>
@@ -1833,7 +2259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>93</v>
       </c>
@@ -1863,7 +2289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
         <v>94</v>
       </c>
@@ -1893,7 +2319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
         <v>95</v>
       </c>
@@ -1921,7 +2347,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
         <v>96</v>
       </c>
@@ -1949,7 +2375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
         <v>97</v>
       </c>
@@ -1977,7 +2403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
         <v>98</v>
       </c>
@@ -2005,7 +2431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
         <v>99</v>
       </c>
@@ -2033,7 +2459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
         <v>100</v>
       </c>
@@ -2061,7 +2487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
         <v>234</v>
       </c>
@@ -2089,7 +2515,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
         <v>101</v>
       </c>
@@ -2117,7 +2543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
         <v>102</v>
       </c>
@@ -2145,7 +2571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
         <v>103</v>
       </c>
@@ -2173,7 +2599,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
         <v>104</v>
       </c>
@@ -2201,7 +2627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
         <v>105</v>
       </c>
@@ -2229,7 +2655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
         <v>106</v>
       </c>
@@ -2257,7 +2683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
         <v>107</v>
       </c>
@@ -2285,7 +2711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
         <v>108</v>
       </c>
@@ -2313,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
         <v>109</v>
       </c>
@@ -2341,7 +2767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
         <v>110</v>
       </c>
@@ -2369,7 +2795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
         <v>111</v>
       </c>
@@ -2397,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
         <v>112</v>
       </c>
@@ -2425,7 +2851,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
         <v>235</v>
       </c>
@@ -2453,7 +2879,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="10" t="s">
         <v>113</v>
       </c>
@@ -2481,7 +2907,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
         <v>114</v>
       </c>
@@ -2509,7 +2935,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
         <v>115</v>
       </c>
@@ -2537,7 +2963,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
         <v>116</v>
       </c>
@@ -2565,7 +2991,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
         <v>117</v>
       </c>
@@ -2593,7 +3019,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
         <v>118</v>
       </c>
@@ -2621,7 +3047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
         <v>119</v>
       </c>
@@ -2649,7 +3075,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
         <v>120</v>
       </c>
@@ -2677,7 +3103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
         <v>121</v>
       </c>
@@ -2705,7 +3131,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
         <v>122</v>
       </c>
@@ -2733,7 +3159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
         <v>123</v>
       </c>
@@ -2761,7 +3187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="10" t="s">
         <v>236</v>
       </c>
@@ -2789,7 +3215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
         <v>124</v>
       </c>
@@ -2817,7 +3243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
         <v>125</v>
       </c>
@@ -2845,7 +3271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
         <v>126</v>
       </c>
@@ -2867,13 +3293,13 @@
         <v>742</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I55" s="5">
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="10" t="s">
         <v>127</v>
       </c>
@@ -2901,7 +3327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="10" t="s">
         <v>128</v>
       </c>
@@ -2929,7 +3355,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
         <v>129</v>
       </c>
@@ -2957,7 +3383,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="10" t="s">
         <v>237</v>
       </c>
@@ -2985,7 +3411,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="10" t="s">
         <v>130</v>
       </c>
@@ -3013,7 +3439,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="10" t="s">
         <v>131</v>
       </c>
@@ -3041,7 +3467,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="10" t="s">
         <v>132</v>
       </c>
@@ -3069,7 +3495,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="10" t="s">
         <v>133</v>
       </c>
@@ -3097,7 +3523,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="10" t="s">
         <v>134</v>
       </c>
@@ -3125,7 +3551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="10" t="s">
         <v>135</v>
       </c>
@@ -3153,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="10" t="s">
         <v>238</v>
       </c>
@@ -3181,7 +3607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="10" t="s">
         <v>239</v>
       </c>
@@ -3203,13 +3629,13 @@
         <v>21.95</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I67" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="10" t="s">
         <v>136</v>
       </c>
@@ -3237,7 +3663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="10" t="s">
         <v>137</v>
       </c>
@@ -3265,7 +3691,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="10" t="s">
         <v>138</v>
       </c>
@@ -3293,7 +3719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="10" t="s">
         <v>139</v>
       </c>
@@ -3321,7 +3747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="10" t="s">
         <v>140</v>
       </c>
@@ -3349,7 +3775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="10" t="s">
         <v>141</v>
       </c>
@@ -3377,7 +3803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="10" t="s">
         <v>142</v>
       </c>
@@ -3405,7 +3831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="12" t="s">
         <v>143</v>
       </c>
@@ -3433,7 +3859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="10" t="s">
         <v>144</v>
       </c>
@@ -3461,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="10" t="s">
         <v>145</v>
       </c>
@@ -3489,7 +3915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="10" t="s">
         <v>146</v>
       </c>
@@ -3517,7 +3943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="10" t="s">
         <v>147</v>
       </c>
@@ -3545,7 +3971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="10" t="s">
         <v>148</v>
       </c>
@@ -3573,7 +3999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="10" t="s">
         <v>149</v>
       </c>
@@ -3582,7 +4008,7 @@
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11">
-        <v>1384</v>
+        <v>754</v>
       </c>
       <c r="E81" s="11">
         <v>0</v>
@@ -3592,7 +4018,7 @@
       </c>
       <c r="G81" s="11">
         <f t="shared" si="2"/>
-        <v>1384</v>
+        <v>754</v>
       </c>
       <c r="H81" s="11" t="s">
         <v>226</v>
@@ -3601,7 +4027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="10" t="s">
         <v>150</v>
       </c>
@@ -3629,7 +4055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="10" t="s">
         <v>151</v>
       </c>
@@ -3657,7 +4083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="10" t="s">
         <v>0</v>
       </c>
@@ -3669,14 +4095,14 @@
         <v>0</v>
       </c>
       <c r="E84" s="11">
-        <v>420</v>
+        <v>642.5</v>
       </c>
       <c r="F84" s="11">
         <v>46</v>
       </c>
       <c r="G84" s="11">
         <f t="shared" si="2"/>
-        <v>486</v>
+        <v>708.5</v>
       </c>
       <c r="H84" s="11" t="s">
         <v>58</v>
@@ -3685,7 +4111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="10" t="s">
         <v>1</v>
       </c>
@@ -3697,14 +4123,14 @@
         <v>0</v>
       </c>
       <c r="E85" s="11">
-        <v>90</v>
+        <v>499.29999999999995</v>
       </c>
       <c r="F85" s="11">
         <v>9.5</v>
       </c>
       <c r="G85" s="11">
         <f t="shared" si="2"/>
-        <v>159.5</v>
+        <v>568.79999999999995</v>
       </c>
       <c r="H85" s="11" t="s">
         <v>59</v>
@@ -3713,7 +4139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="10" t="s">
         <v>2</v>
       </c>
@@ -3725,14 +4151,14 @@
         <v>0</v>
       </c>
       <c r="E86" s="11">
-        <v>120</v>
+        <v>302.5</v>
       </c>
       <c r="F86" s="11">
         <v>37</v>
       </c>
       <c r="G86" s="11">
         <f t="shared" si="2"/>
-        <v>177</v>
+        <v>359.5</v>
       </c>
       <c r="H86" s="11" t="s">
         <v>60</v>
@@ -3741,7 +4167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="10" t="s">
         <v>3</v>
       </c>
@@ -3753,14 +4179,14 @@
         <v>0</v>
       </c>
       <c r="E87" s="11">
-        <v>480</v>
+        <v>380</v>
       </c>
       <c r="F87" s="11">
         <v>30</v>
       </c>
       <c r="G87" s="11">
         <f t="shared" si="2"/>
-        <v>570</v>
+        <v>470</v>
       </c>
       <c r="H87" s="11" t="s">
         <v>61</v>
@@ -3769,7 +4195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="10" t="s">
         <v>4</v>
       </c>
@@ -3797,7 +4223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="10" t="s">
         <v>5</v>
       </c>
@@ -3809,14 +4235,14 @@
         <v>89</v>
       </c>
       <c r="E89" s="11">
-        <v>411.7</v>
+        <v>381.7</v>
       </c>
       <c r="F89" s="11">
         <v>24</v>
       </c>
       <c r="G89" s="11">
         <f t="shared" si="2"/>
-        <v>524.70000000000005</v>
+        <v>494.7</v>
       </c>
       <c r="H89" s="11" t="s">
         <v>63</v>
@@ -3825,7 +4251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="10" t="s">
         <v>6</v>
       </c>
@@ -3837,14 +4263,14 @@
         <v>0</v>
       </c>
       <c r="E90" s="11">
-        <v>30</v>
+        <v>262.5</v>
       </c>
       <c r="F90" s="11">
         <v>10.5</v>
       </c>
       <c r="G90" s="11">
         <f t="shared" si="2"/>
-        <v>60.5</v>
+        <v>293</v>
       </c>
       <c r="H90" s="11" t="s">
         <v>64</v>
@@ -3853,7 +4279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="10" t="s">
         <v>7</v>
       </c>
@@ -3881,7 +4307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="10" t="s">
         <v>8</v>
       </c>
@@ -3909,7 +4335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="10" t="s">
         <v>9</v>
       </c>
@@ -3937,7 +4363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="10" t="s">
         <v>10</v>
       </c>
@@ -3965,7 +4391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="10" t="s">
         <v>11</v>
       </c>
@@ -3993,7 +4419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="10" t="s">
         <v>12</v>
       </c>
@@ -4015,13 +4441,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I96" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="10" t="s">
         <v>13</v>
       </c>
@@ -4033,14 +4459,14 @@
         <v>0</v>
       </c>
       <c r="E97" s="11">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F97" s="11">
         <v>27</v>
       </c>
       <c r="G97" s="11">
         <f t="shared" si="2"/>
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H97" s="11" t="s">
         <v>227</v>
@@ -4049,7 +4475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="10" t="s">
         <v>14</v>
       </c>
@@ -4077,7 +4503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="10" t="s">
         <v>15</v>
       </c>
@@ -4105,7 +4531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="10" t="s">
         <v>16</v>
       </c>
@@ -4133,7 +4559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="10" t="s">
         <v>17</v>
       </c>
@@ -4151,7 +4577,7 @@
         <v>200</v>
       </c>
       <c r="G101" s="11">
-        <f t="shared" ref="G101:G131" si="3">SUM(B101:F101)</f>
+        <f t="shared" ref="G101:G130" si="3">SUM(B101:F101)</f>
         <v>44700</v>
       </c>
       <c r="H101" s="11" t="s">
@@ -4161,7 +4587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="10" t="s">
         <v>18</v>
       </c>
@@ -4189,7 +4615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="10" t="s">
         <v>19</v>
       </c>
@@ -4211,13 +4637,13 @@
         <v>260</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I103" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="10" t="s">
         <v>20</v>
       </c>
@@ -4239,13 +4665,13 @@
         <v>68.599999999999994</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I104" s="5">
         <v>1091</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="10" t="s">
         <v>21</v>
       </c>
@@ -4267,13 +4693,13 @@
         <v>51.900000000000006</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I105" s="5">
         <v>1090</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="10" t="s">
         <v>22</v>
       </c>
@@ -4299,7 +4725,7 @@
       </c>
       <c r="I106" s="5"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="10" t="s">
         <v>23</v>
       </c>
@@ -4325,7 +4751,7 @@
       </c>
       <c r="I107" s="5"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="10" t="s">
         <v>24</v>
       </c>
@@ -4351,7 +4777,7 @@
       </c>
       <c r="I108" s="5"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="10" t="s">
         <v>25</v>
       </c>
@@ -4377,7 +4803,7 @@
       </c>
       <c r="I109" s="5"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="10" t="s">
         <v>26</v>
       </c>
@@ -4403,7 +4829,7 @@
       </c>
       <c r="I110" s="5"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="10" t="s">
         <v>27</v>
       </c>
@@ -4415,21 +4841,21 @@
         <v>0</v>
       </c>
       <c r="E111" s="11">
-        <v>566</v>
+        <v>476</v>
       </c>
       <c r="F111" s="11">
         <v>26</v>
       </c>
       <c r="G111" s="11">
         <f t="shared" si="3"/>
-        <v>673.5</v>
+        <v>583.5</v>
       </c>
       <c r="H111" s="11">
         <v>0</v>
       </c>
       <c r="I111" s="5"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="10" t="s">
         <v>28</v>
       </c>
@@ -4455,7 +4881,7 @@
       </c>
       <c r="I112" s="5"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="10" t="s">
         <v>29</v>
       </c>
@@ -4481,7 +4907,7 @@
       </c>
       <c r="I113" s="5"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="10" t="s">
         <v>30</v>
       </c>
@@ -4507,7 +4933,7 @@
       </c>
       <c r="I114" s="5"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="10" t="s">
         <v>31</v>
       </c>
@@ -4533,7 +4959,7 @@
       </c>
       <c r="I115" s="5"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="10" t="s">
         <v>32</v>
       </c>
@@ -4545,21 +4971,21 @@
         <v>0</v>
       </c>
       <c r="E116" s="11">
-        <v>231.65</v>
+        <v>198.25</v>
       </c>
       <c r="F116" s="11">
         <v>120</v>
       </c>
       <c r="G116" s="11">
         <f t="shared" si="3"/>
-        <v>359.95000000000005</v>
+        <v>326.55</v>
       </c>
       <c r="H116" s="11">
         <v>0</v>
       </c>
       <c r="I116" s="5"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="10" t="s">
         <v>33</v>
       </c>
@@ -4571,21 +4997,21 @@
         <v>0</v>
       </c>
       <c r="E117" s="11">
-        <v>463.35</v>
+        <v>421.75</v>
       </c>
       <c r="F117" s="11">
         <v>53</v>
       </c>
       <c r="G117" s="11">
         <f t="shared" si="3"/>
-        <v>532.95000000000005</v>
+        <v>491.35</v>
       </c>
       <c r="H117" s="11">
         <v>0</v>
       </c>
       <c r="I117" s="5"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="10" t="s">
         <v>34</v>
       </c>
@@ -4597,21 +5023,21 @@
         <v>0</v>
       </c>
       <c r="E118" s="11">
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="F118" s="11">
         <v>18</v>
       </c>
       <c r="G118" s="11">
         <f t="shared" si="3"/>
-        <v>768</v>
+        <v>708</v>
       </c>
       <c r="H118" s="11">
         <v>0</v>
       </c>
       <c r="I118" s="5"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="10" t="s">
         <v>35</v>
       </c>
@@ -4623,21 +5049,21 @@
         <v>0</v>
       </c>
       <c r="E119" s="11">
-        <v>774.3</v>
+        <v>743.5</v>
       </c>
       <c r="F119" s="11">
         <v>19</v>
       </c>
       <c r="G119" s="11">
         <f t="shared" si="3"/>
-        <v>823.3</v>
+        <v>792.5</v>
       </c>
       <c r="H119" s="11">
         <v>0</v>
       </c>
       <c r="I119" s="5"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="10" t="s">
         <v>36</v>
       </c>
@@ -4649,21 +5075,21 @@
         <v>0</v>
       </c>
       <c r="E120" s="11">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="F120" s="11">
         <v>21.8</v>
       </c>
       <c r="G120" s="11">
         <f t="shared" si="3"/>
-        <v>274.8</v>
+        <v>184.8</v>
       </c>
       <c r="H120" s="11">
         <v>0</v>
       </c>
       <c r="I120" s="5"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="10" t="s">
         <v>37</v>
       </c>
@@ -4689,7 +5115,7 @@
       </c>
       <c r="I121" s="5"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="10" t="s">
         <v>38</v>
       </c>
@@ -4715,9 +5141,9 @@
       </c>
       <c r="I122" s="5"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="10" t="s">
-        <v>240</v>
+        <v>39</v>
       </c>
       <c r="B123" s="11">
         <v>0</v>
@@ -4730,20 +5156,20 @@
         <v>0</v>
       </c>
       <c r="F123" s="11">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="G123" s="11">
         <f t="shared" si="3"/>
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="H123" s="11">
         <v>0</v>
       </c>
       <c r="I123" s="5"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B124" s="11">
         <v>0</v>
@@ -4756,20 +5182,20 @@
         <v>0</v>
       </c>
       <c r="F124" s="11">
-        <v>0</v>
+        <v>1073</v>
       </c>
       <c r="G124" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1073</v>
       </c>
       <c r="H124" s="11">
         <v>0</v>
       </c>
       <c r="I124" s="5"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B125" s="11">
         <v>0</v>
@@ -4782,23 +5208,23 @@
         <v>0</v>
       </c>
       <c r="F125" s="11">
-        <v>1073</v>
+        <v>0</v>
       </c>
       <c r="G125" s="11">
         <f t="shared" si="3"/>
-        <v>1073</v>
+        <v>0</v>
       </c>
       <c r="H125" s="11">
         <v>0</v>
       </c>
       <c r="I125" s="5"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B126" s="11">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="C126" s="11"/>
       <c r="D126" s="11">
@@ -4812,45 +5238,45 @@
       </c>
       <c r="G126" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="H126" s="11">
         <v>0</v>
       </c>
       <c r="I126" s="5"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B127" s="11">
-        <v>11.8</v>
+        <v>11.25</v>
       </c>
       <c r="C127" s="11"/>
       <c r="D127" s="11">
         <v>0</v>
       </c>
       <c r="E127" s="11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F127" s="11">
-        <v>0</v>
+        <v>1.6279999999999999</v>
       </c>
       <c r="G127" s="11">
         <f t="shared" si="3"/>
-        <v>11.8</v>
+        <v>112.878</v>
       </c>
       <c r="H127" s="11">
         <v>0</v>
       </c>
       <c r="I127" s="5"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B128" s="11">
-        <v>11.25</v>
+        <v>25</v>
       </c>
       <c r="C128" s="11"/>
       <c r="D128" s="11">
@@ -4860,179 +5286,179 @@
         <v>100</v>
       </c>
       <c r="F128" s="11">
-        <v>1.6279999999999999</v>
+        <v>3.6300000000000003</v>
       </c>
       <c r="G128" s="11">
         <f t="shared" si="3"/>
-        <v>112.878</v>
+        <v>128.63</v>
       </c>
       <c r="H128" s="11">
         <v>0</v>
       </c>
       <c r="I128" s="5"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B129" s="11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C129" s="11"/>
       <c r="D129" s="11">
         <v>0</v>
       </c>
       <c r="E129" s="11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F129" s="11">
-        <v>3.6300000000000003</v>
+        <v>0</v>
       </c>
       <c r="G129" s="11">
         <f t="shared" si="3"/>
-        <v>128.63</v>
+        <v>0</v>
       </c>
       <c r="H129" s="11">
         <v>0</v>
       </c>
       <c r="I129" s="5"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B130" s="11">
         <v>0</v>
       </c>
       <c r="C130" s="11"/>
       <c r="D130" s="11">
-        <v>0</v>
+        <v>7130</v>
       </c>
       <c r="E130" s="11">
         <v>0</v>
       </c>
       <c r="F130" s="11">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="G130" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7458</v>
       </c>
       <c r="H130" s="11">
         <v>0</v>
       </c>
       <c r="I130" s="5"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B131" s="11">
         <v>0</v>
       </c>
       <c r="C131" s="11"/>
       <c r="D131" s="11">
-        <v>2955</v>
+        <v>2300</v>
       </c>
       <c r="E131" s="11">
         <v>0</v>
       </c>
       <c r="F131" s="11">
-        <v>328</v>
+        <v>100</v>
       </c>
       <c r="G131" s="11">
-        <f t="shared" si="3"/>
-        <v>3283</v>
+        <f t="shared" ref="G131:G145" si="4">SUM(B131:F131)</f>
+        <v>2400</v>
       </c>
       <c r="H131" s="11">
         <v>0</v>
       </c>
       <c r="I131" s="5"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B132" s="11">
         <v>0</v>
       </c>
       <c r="C132" s="11"/>
       <c r="D132" s="11">
-        <v>2405</v>
+        <v>2148</v>
       </c>
       <c r="E132" s="11">
         <v>0</v>
       </c>
       <c r="F132" s="11">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="G132" s="11">
-        <f t="shared" ref="G132:G146" si="4">SUM(B132:F132)</f>
-        <v>2505</v>
+        <f t="shared" si="4"/>
+        <v>2203</v>
       </c>
       <c r="H132" s="11">
         <v>0</v>
       </c>
       <c r="I132" s="5"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B133" s="11">
         <v>0</v>
       </c>
       <c r="C133" s="11"/>
       <c r="D133" s="11">
-        <v>275</v>
+        <v>4055</v>
       </c>
       <c r="E133" s="11">
         <v>0</v>
       </c>
       <c r="F133" s="11">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="G133" s="11">
         <f t="shared" si="4"/>
-        <v>330</v>
+        <v>4185</v>
       </c>
       <c r="H133" s="11">
         <v>0</v>
       </c>
       <c r="I133" s="5"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B134" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C134" s="11"/>
       <c r="D134" s="11">
-        <v>2115</v>
+        <v>0</v>
       </c>
       <c r="E134" s="11">
         <v>0</v>
       </c>
       <c r="F134" s="11">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="G134" s="11">
         <f t="shared" si="4"/>
-        <v>2245</v>
+        <v>2</v>
       </c>
       <c r="H134" s="11">
         <v>0</v>
       </c>
       <c r="I134" s="5"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B135" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C135" s="11"/>
       <c r="D135" s="11">
@@ -5046,16 +5472,16 @@
       </c>
       <c r="G135" s="11">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135" s="11">
         <v>0</v>
       </c>
       <c r="I135" s="5"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B136" s="11">
         <v>0</v>
@@ -5079,9 +5505,9 @@
       </c>
       <c r="I136" s="5"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B137" s="11">
         <v>0</v>
@@ -5094,20 +5520,20 @@
         <v>0</v>
       </c>
       <c r="F137" s="11">
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="G137" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="H137" s="11">
         <v>0</v>
       </c>
       <c r="I137" s="5"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B138" s="11">
         <v>0</v>
@@ -5120,23 +5546,23 @@
         <v>0</v>
       </c>
       <c r="F138" s="11">
-        <v>442</v>
+        <v>258</v>
       </c>
       <c r="G138" s="11">
         <f t="shared" si="4"/>
-        <v>442</v>
+        <v>258</v>
       </c>
       <c r="H138" s="11">
         <v>0</v>
       </c>
       <c r="I138" s="5"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="10" t="s">
-        <v>54</v>
+        <v>246</v>
       </c>
       <c r="B139" s="11">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C139" s="11"/>
       <c r="D139" s="11">
@@ -5146,23 +5572,23 @@
         <v>0</v>
       </c>
       <c r="F139" s="11">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="G139" s="11">
         <f t="shared" si="4"/>
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="H139" s="11">
         <v>0</v>
       </c>
       <c r="I139" s="5"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="10" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B140" s="11">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="C140" s="11"/>
       <c r="D140" s="11">
@@ -5176,19 +5602,19 @@
       </c>
       <c r="G140" s="11">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="H140" s="11">
         <v>0</v>
       </c>
       <c r="I140" s="5"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="10" t="s">
-        <v>241</v>
+        <v>70</v>
       </c>
       <c r="B141" s="11">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C141" s="11"/>
       <c r="D141" s="11">
@@ -5202,19 +5628,19 @@
       </c>
       <c r="G141" s="11">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H141" s="11">
         <v>0</v>
       </c>
       <c r="I141" s="5"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B142" s="11">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C142" s="11"/>
       <c r="D142" s="11">
@@ -5228,16 +5654,16 @@
       </c>
       <c r="G142" s="11">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H142" s="11">
         <v>0</v>
       </c>
       <c r="I142" s="5"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B143" s="11">
         <v>1</v>
@@ -5261,12 +5687,12 @@
       </c>
       <c r="I143" s="5"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B144" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144" s="11"/>
       <c r="D144" s="11">
@@ -5280,19 +5706,19 @@
       </c>
       <c r="G144" s="11">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H144" s="11">
         <v>0</v>
       </c>
       <c r="I144" s="5"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="10" t="s">
-        <v>73</v>
+        <v>241</v>
       </c>
       <c r="B145" s="11">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C145" s="11"/>
       <c r="D145" s="11">
@@ -5306,19 +5732,19 @@
       </c>
       <c r="G145" s="11">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H145" s="11">
         <v>0</v>
       </c>
       <c r="I145" s="5"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="10" t="s">
-        <v>242</v>
+        <v>58</v>
       </c>
       <c r="B146" s="11">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="C146" s="11"/>
       <c r="D146" s="11">
@@ -5331,20 +5757,19 @@
         <v>0</v>
       </c>
       <c r="G146" s="11">
-        <f t="shared" si="4"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H146" s="11">
         <v>0</v>
       </c>
       <c r="I146" s="5"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B147" s="11">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="C147" s="11"/>
       <c r="D147" s="11">
@@ -5364,9 +5789,9 @@
       </c>
       <c r="I147" s="5"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B148" s="11">
         <v>0</v>
@@ -5389,12 +5814,12 @@
       </c>
       <c r="I148" s="5"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B149" s="11">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="C149" s="11"/>
       <c r="D149" s="11">
@@ -5414,43 +5839,43 @@
       </c>
       <c r="I149" s="5"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B150" s="11">
-        <v>6.5</v>
-      </c>
-      <c r="C150" s="11"/>
+        <v>0</v>
+      </c>
+      <c r="C150" s="13"/>
       <c r="D150" s="11">
         <v>0</v>
       </c>
       <c r="E150" s="11">
         <v>0</v>
       </c>
-      <c r="F150" s="11">
-        <v>0</v>
-      </c>
-      <c r="G150" s="11">
-        <v>0</v>
-      </c>
-      <c r="H150" s="11">
-        <v>0</v>
-      </c>
-      <c r="I150" s="5"/>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F150" s="13">
+        <v>0</v>
+      </c>
+      <c r="G150" s="13">
+        <v>0</v>
+      </c>
+      <c r="H150" s="13">
+        <v>0</v>
+      </c>
+      <c r="I150" s="7"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="10" t="s">
-        <v>69</v>
+        <v>245</v>
       </c>
       <c r="B151" s="11">
         <v>0</v>
       </c>
       <c r="C151" s="13"/>
-      <c r="D151" s="13">
-        <v>0</v>
-      </c>
-      <c r="E151" s="13">
+      <c r="D151" s="11">
+        <v>0</v>
+      </c>
+      <c r="E151" s="11">
         <v>0</v>
       </c>
       <c r="F151" s="13">
@@ -5464,58 +5889,34 @@
       </c>
       <c r="I151" s="7"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A152" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B152" s="11">
-        <v>0</v>
-      </c>
-      <c r="C152" s="13"/>
-      <c r="D152" s="13">
-        <v>0</v>
-      </c>
-      <c r="E152" s="13">
-        <v>0</v>
-      </c>
-      <c r="F152" s="13">
-        <v>0</v>
-      </c>
-      <c r="G152" s="13">
-        <v>0</v>
-      </c>
-      <c r="H152" s="13">
-        <v>0</v>
-      </c>
-      <c r="I152" s="7"/>
-    </row>
-    <row r="153" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="B153" s="14">
+    <row r="152" spans="1:9" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="B152" s="14">
         <v>7</v>
       </c>
-      <c r="C153" s="15"/>
-      <c r="D153" s="15">
-        <v>0</v>
-      </c>
-      <c r="E153" s="15">
-        <v>0</v>
-      </c>
-      <c r="F153" s="15">
-        <v>0</v>
-      </c>
-      <c r="G153" s="15">
-        <v>0</v>
-      </c>
-      <c r="H153" s="15">
-        <v>0</v>
-      </c>
-      <c r="I153" s="8"/>
+      <c r="C152" s="15"/>
+      <c r="D152" s="14">
+        <v>0</v>
+      </c>
+      <c r="E152" s="14">
+        <v>0</v>
+      </c>
+      <c r="F152" s="15">
+        <v>0</v>
+      </c>
+      <c r="G152" s="15">
+        <v>0</v>
+      </c>
+      <c r="H152" s="15">
+        <v>0</v>
+      </c>
+      <c r="I152" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H375" xr:uid="{69590074-F9E1-47CB-9D65-9D1D53B05140}"/>
+  <sheetProtection autoFilter="0"/>
+  <autoFilter ref="A4:H374" xr:uid="{69590074-F9E1-47CB-9D65-9D1D53B05140}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/جر د شهر 8.xlsx
+++ b/جر د شهر 8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\جرد شهر 8\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{031788DC-5BC8-CF41-AF19-40EAABFD6849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F30C20CE-F7F3-2D4E-92EE-E58FEDE74F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" xr2:uid="{86282878-4084-4E7F-B814-2BEB8919EF4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{86282878-4084-4E7F-B814-2BEB8919EF4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="261">
   <si>
     <t>اكياس برجر الهنا ص</t>
   </si>
@@ -113,9 +113,6 @@
     <t>اكياس كبده 3ك</t>
   </si>
   <si>
-    <t>كروت مفروم صويا ازرق 350</t>
-  </si>
-  <si>
     <t>كروت مفروم صافي 350</t>
   </si>
   <si>
@@ -128,673 +125,703 @@
     <t>اكياس s.p شفاف برجر</t>
   </si>
   <si>
+    <t>اكياس سجق s.p صغير</t>
+  </si>
+  <si>
+    <t>اكياس سجق s.p كبير</t>
+  </si>
+  <si>
+    <t>اكياس برجر s.p صغير</t>
+  </si>
+  <si>
+    <t>اكياس كفته s.p صغير</t>
+  </si>
+  <si>
+    <t>اكياس كفته s.p كبير</t>
+  </si>
+  <si>
+    <t>اكياس برجر s.p كبير</t>
+  </si>
+  <si>
+    <t>اكياس بانيه s.p</t>
+  </si>
+  <si>
+    <t>طبق مسطح 1/2 شفاف</t>
+  </si>
+  <si>
+    <t>كراتين s.p ابيض</t>
+  </si>
+  <si>
+    <t>علب بلاستيك شفاف</t>
+  </si>
+  <si>
+    <t>اكياس كفته 3ك ابوهاشم</t>
+  </si>
+  <si>
+    <t>أكياس استربس الهنا ص</t>
+  </si>
+  <si>
+    <t>اكياس عجينه بقري 5كيلو اسبيشيال</t>
+  </si>
+  <si>
+    <t>اكياس سجق اسبيشيال كيلو5</t>
+  </si>
+  <si>
+    <t>اكياس عرض نايلون(60*90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كراتين الهنا ازرق </t>
+  </si>
+  <si>
+    <t xml:space="preserve">كراتين الهنا اخضر </t>
+  </si>
+  <si>
+    <t>كراتين اسبشيال احمر</t>
+  </si>
+  <si>
+    <t>كراتين اسبشيال اسود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مذيب </t>
+  </si>
+  <si>
+    <t>اكياس 40 * 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">برانيك صويا </t>
+  </si>
+  <si>
+    <t>برنيك برجر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">برنيك سجق </t>
+  </si>
+  <si>
+    <t>ممبار</t>
+  </si>
+  <si>
+    <t>خام عجينة سجق أبو هاشم</t>
+  </si>
+  <si>
+    <t>خام عجينة كفته أبو هاشم</t>
+  </si>
+  <si>
+    <t>خام عجينة برجر  أبو هاشم</t>
+  </si>
+  <si>
+    <t>خام مفروم صافى 5ك</t>
+  </si>
+  <si>
+    <t>خام عجينة برجر  اسبيشيال</t>
+  </si>
+  <si>
+    <t>خاج عجينة كفته اسبيشيال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خام مفروم اسبيشيال </t>
+  </si>
+  <si>
+    <t xml:space="preserve">خام عجينه بقري اسبيشيال </t>
+  </si>
+  <si>
+    <t xml:space="preserve">خام عجينه مفروم صويا </t>
+  </si>
+  <si>
+    <t>خام عجينه سجق اسبيشيال</t>
+  </si>
+  <si>
+    <t>خام مفروم صويا الهنا</t>
+  </si>
+  <si>
+    <t>خام عجينة برجر  الهنا</t>
+  </si>
+  <si>
+    <t>خام عجينة كفته الهنا</t>
+  </si>
+  <si>
+    <t>خام عجينة سجق الهنا</t>
+  </si>
+  <si>
+    <t>فلاتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استطوانة فريون </t>
+  </si>
+  <si>
+    <t xml:space="preserve">زيت سيارات </t>
+  </si>
+  <si>
+    <t>اسم الصنف</t>
+  </si>
+  <si>
+    <t>الرصيد النهائي المصنع</t>
+  </si>
+  <si>
+    <t>الرصيد النهائي النهضه</t>
+  </si>
+  <si>
+    <t>الرصيد النهائي المنوفية</t>
+  </si>
+  <si>
+    <t>الرصيد النهائي التغليف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بصل </t>
+  </si>
+  <si>
+    <t>ثوم</t>
+  </si>
+  <si>
+    <t>فلفل بارد</t>
+  </si>
+  <si>
+    <t>مفروم فراخ شعبي</t>
+  </si>
+  <si>
+    <t>صميد</t>
+  </si>
+  <si>
+    <t>صويا لحمه</t>
+  </si>
+  <si>
+    <t>صويا اوزيليت</t>
+  </si>
+  <si>
+    <t>مفروم فراخ فاخر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دهن بلدي </t>
+  </si>
+  <si>
+    <t>لحم كتف</t>
+  </si>
+  <si>
+    <t>لحم رقبه</t>
+  </si>
+  <si>
+    <t>لحم سن</t>
+  </si>
+  <si>
+    <t>لحمه ارباع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سمانة هندي </t>
+  </si>
+  <si>
+    <t>برغل</t>
+  </si>
+  <si>
+    <t>صويا  فراخ</t>
+  </si>
+  <si>
+    <t>كبده</t>
+  </si>
+  <si>
+    <t>جلد</t>
+  </si>
+  <si>
+    <t>هانك</t>
+  </si>
+  <si>
+    <t>دوبريه</t>
+  </si>
+  <si>
+    <t>فلفل رومي حامي</t>
+  </si>
+  <si>
+    <t>بقسماط اصفر</t>
+  </si>
+  <si>
+    <t>بقسماط ابيض</t>
+  </si>
+  <si>
+    <t>بطاطس</t>
+  </si>
+  <si>
+    <t>دوبرية بسطرمة (لحمة)</t>
+  </si>
+  <si>
+    <t>قلب برازيلي</t>
+  </si>
+  <si>
+    <t>بوش</t>
+  </si>
+  <si>
+    <t>شعريه</t>
+  </si>
+  <si>
+    <t>دقيق</t>
+  </si>
+  <si>
+    <t>نشا</t>
+  </si>
+  <si>
+    <t>فلفل اسود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قرنفل </t>
+  </si>
+  <si>
+    <t xml:space="preserve">كمون </t>
+  </si>
+  <si>
+    <t>كبابه</t>
+  </si>
+  <si>
+    <t>بقدونس</t>
+  </si>
+  <si>
+    <t>لورا</t>
+  </si>
+  <si>
+    <t>خلنجان</t>
+  </si>
+  <si>
+    <t>كزبره</t>
+  </si>
+  <si>
+    <t>قرفه</t>
+  </si>
+  <si>
+    <t>زعتر</t>
+  </si>
+  <si>
+    <t>شطه</t>
+  </si>
+  <si>
+    <t>جوزه الطيب</t>
+  </si>
+  <si>
+    <t>ينسون</t>
+  </si>
+  <si>
+    <t>حبهان</t>
+  </si>
+  <si>
+    <t>بابريكا</t>
+  </si>
+  <si>
+    <t>جنزبيل</t>
+  </si>
+  <si>
+    <t>الملح</t>
+  </si>
+  <si>
+    <t>فوسفات</t>
+  </si>
+  <si>
+    <t>جلتومات</t>
+  </si>
+  <si>
+    <t>طعم سجق بودر</t>
+  </si>
+  <si>
+    <t>طعم ليه</t>
+  </si>
+  <si>
+    <t>طعم كفته</t>
+  </si>
+  <si>
+    <t>طعم برجر</t>
+  </si>
+  <si>
+    <t>طعم بيف</t>
+  </si>
+  <si>
+    <t>طعم شواي</t>
+  </si>
+  <si>
+    <t>طعم دخان</t>
+  </si>
+  <si>
+    <t>سكر</t>
+  </si>
+  <si>
+    <t>فلفل ابيض</t>
+  </si>
+  <si>
+    <t>لون طبيعي</t>
+  </si>
+  <si>
+    <t>طعم فراخ</t>
+  </si>
+  <si>
+    <t>زيوت بسطرمه</t>
+  </si>
+  <si>
+    <t>ثوم بودر</t>
+  </si>
+  <si>
+    <t>كامينا</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
+    <t>زيت سجق</t>
+  </si>
+  <si>
+    <t>كمينا ابيض</t>
+  </si>
+  <si>
+    <t>اكياس افيز</t>
+  </si>
+  <si>
+    <t>لازق</t>
+  </si>
+  <si>
+    <t>كراتين ابوهاشم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ورق برجر </t>
+  </si>
+  <si>
+    <t xml:space="preserve">مزيل لماكينة التغليف </t>
+  </si>
+  <si>
+    <t>الإجمالي</t>
+  </si>
+  <si>
+    <t>مفروم ابو هاشم 350</t>
+  </si>
+  <si>
+    <t>مفروم صافي ابوهاشم 500</t>
+  </si>
+  <si>
+    <t>كبده اسكندراني 370</t>
+  </si>
+  <si>
+    <t>سجق ابوهاشم 3ك</t>
+  </si>
+  <si>
+    <t>سجق ابوهاشم 1ك</t>
+  </si>
+  <si>
+    <t>سجق ابوهاشم 800</t>
+  </si>
+  <si>
+    <t>سجق ابوهاشم 350</t>
+  </si>
+  <si>
+    <t>كفته ابوهاشم 800</t>
+  </si>
+  <si>
+    <t>كفته ابوهاشم 350</t>
+  </si>
+  <si>
+    <t>برجر ابوهاشم 1.5</t>
+  </si>
+  <si>
+    <t>برجر ابوهاشم1100</t>
+  </si>
+  <si>
+    <t>برجر ابو هاشم 800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">برجر ابوهاشم 600 </t>
+  </si>
+  <si>
+    <t>برجر ابوهاشم 400</t>
+  </si>
+  <si>
+    <t>شاورما  400</t>
+  </si>
+  <si>
+    <t>بفتيك 400</t>
+  </si>
+  <si>
+    <t>قطع  400</t>
+  </si>
+  <si>
+    <t>قطع 800</t>
+  </si>
+  <si>
+    <t>مفروم ابو هاشم 3 ك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سجق ابو هاشم 2 ك </t>
+  </si>
+  <si>
+    <t xml:space="preserve">كبده امريكي3 ك </t>
+  </si>
+  <si>
+    <t>مفروم صويا-بروتين  400 ش</t>
+  </si>
+  <si>
+    <t>مفروم صويا-بروتين 400 علب</t>
+  </si>
+  <si>
+    <t>برجر ابوهاشم 1200</t>
+  </si>
+  <si>
+    <t>كبده اك</t>
+  </si>
+  <si>
+    <t>برجر ابوهاشم 1000</t>
+  </si>
+  <si>
+    <t>عجينة سجق ابوهاشم 1ك</t>
+  </si>
+  <si>
+    <t>عجينة كفته ابو هاشم 5 ك</t>
+  </si>
+  <si>
+    <t>كفتة ابو هاشم 1ك</t>
+  </si>
+  <si>
+    <t>كيس كبده 3 ك برازيلي</t>
+  </si>
+  <si>
+    <t>سجق ابو هاشم 1.5 ك</t>
+  </si>
+  <si>
+    <t>عجينة سجق ابوهاشم 3ك</t>
+  </si>
+  <si>
+    <t>كبده  500</t>
+  </si>
+  <si>
+    <t>سجق الهنا 700</t>
+  </si>
+  <si>
+    <t>سجق الهنا 300</t>
+  </si>
+  <si>
+    <t>كفته الهنا 800</t>
+  </si>
+  <si>
+    <t>كفته الهنا 350</t>
+  </si>
+  <si>
+    <t>برجر الهنا 800</t>
+  </si>
+  <si>
+    <t>برجر الهنا 900</t>
+  </si>
+  <si>
+    <t>برجر الهنا 350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سجق الهنا 3 ك </t>
+  </si>
+  <si>
+    <t xml:space="preserve">سجق الهنا 5 ك </t>
+  </si>
+  <si>
+    <t xml:space="preserve">بانيه 700 </t>
+  </si>
+  <si>
+    <t>بانيه 800</t>
+  </si>
+  <si>
+    <t>بانيه 900</t>
+  </si>
+  <si>
+    <t>عجينه سجق هنا 5ك</t>
+  </si>
+  <si>
+    <t>سجق الهنا عرض 200ج</t>
+  </si>
+  <si>
+    <t>برجر الهنا عرض 300ج</t>
+  </si>
+  <si>
+    <t>كفتة الهنا عرض 200ج</t>
+  </si>
+  <si>
+    <t>عرض ثلاثي الهنا&lt;سجق برجر كفته &gt;</t>
+  </si>
+  <si>
+    <t>برجر اسبيشيال1ك</t>
+  </si>
+  <si>
+    <t>برجر اسبيشيال 400</t>
+  </si>
+  <si>
+    <t>كفته اسبيشيال 900</t>
+  </si>
+  <si>
+    <t>كفته اسبيشيال 350</t>
+  </si>
+  <si>
+    <t>سجق اسبيشيال 700</t>
+  </si>
+  <si>
+    <t>سجق اسبيشيال300</t>
+  </si>
+  <si>
+    <t>بانيه اسبيشيال900</t>
+  </si>
+  <si>
+    <t>بانيه اسبيشيال 800</t>
+  </si>
+  <si>
+    <t>بانيه اسبيشيال حار800</t>
+  </si>
+  <si>
+    <t>سجق اسبشيال 5ك</t>
+  </si>
+  <si>
+    <t>مفروم اسبيشيال 400</t>
+  </si>
+  <si>
+    <t>عجينه بقري اسبيشيال 5 كيلو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عجينه مفروم صويا </t>
+  </si>
+  <si>
+    <t>كبده اسبيشيال 400</t>
+  </si>
+  <si>
+    <t>برجر مخصوص</t>
+  </si>
+  <si>
+    <t>كفتة مخصوص</t>
+  </si>
+  <si>
+    <t>سجق مخصوص 1ك</t>
+  </si>
+  <si>
+    <t>عرض ثلاثي &lt;سجق برجر كفته 700جرام&gt;</t>
+  </si>
+  <si>
+    <t>عجينه بقري اسبيشيال 500جرام</t>
+  </si>
+  <si>
+    <t>بانيه 5كيلو حار</t>
+  </si>
+  <si>
+    <t>عجينة بقرى 250ج</t>
+  </si>
+  <si>
+    <t>مفروم صافى 5ك</t>
+  </si>
+  <si>
+    <t>موزة فرخة</t>
+  </si>
+  <si>
+    <t>بانيه بارد دوفا</t>
+  </si>
+  <si>
+    <t>لحمة قطع كيلو أبو هاشم</t>
+  </si>
+  <si>
+    <t>كبده اسبيشيال 3 ك</t>
+  </si>
+  <si>
+    <t>بفتيك 600</t>
+  </si>
+  <si>
+    <t>عجينة كفته الهنا الـ5 ك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عجينة بقري 1 ك </t>
+  </si>
+  <si>
+    <t xml:space="preserve">عجينة بقري 3 ك </t>
+  </si>
+  <si>
+    <t>النفق</t>
+  </si>
+  <si>
+    <t>فيليه</t>
+  </si>
+  <si>
+    <t>كرفس</t>
+  </si>
+  <si>
+    <t>روزماري</t>
+  </si>
+  <si>
+    <t>بصل بودر</t>
+  </si>
+  <si>
+    <t>كربوناتو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شرش بودر </t>
+  </si>
+  <si>
+    <t xml:space="preserve">حشوة زيت </t>
+  </si>
+  <si>
+    <t>استبربس SP 900</t>
+  </si>
+  <si>
+    <t>استبربس 800</t>
+  </si>
+  <si>
+    <t>استبربس GB 2</t>
+  </si>
+  <si>
+    <t>بانيه 1 ك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كفته أبو هاشم 1 ك </t>
+  </si>
+  <si>
+    <t>استربس 1 ك</t>
+  </si>
+  <si>
+    <t>جرد شهر 8 لعام 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كروت برجر أبو هاشم </t>
+  </si>
+  <si>
+    <t>فلانك + مجمل رصيد اللحمة بالنفق</t>
+  </si>
+  <si>
+    <t>كروت كبده علب 350</t>
+  </si>
+  <si>
+    <t>كروت استربس</t>
+  </si>
+  <si>
     <t>اكياس برجر ابوهاشم 1ك</t>
   </si>
   <si>
-    <t>اكياس سجق s.p صغير</t>
-  </si>
-  <si>
-    <t>اكياس سجق s.p كبير</t>
-  </si>
-  <si>
-    <t>اكياس برجر s.p صغير</t>
-  </si>
-  <si>
-    <t>اكياس كفته s.p صغير</t>
-  </si>
-  <si>
-    <t>اكياس كفته s.p كبير</t>
-  </si>
-  <si>
-    <t>اكياس برجر s.p كبير</t>
-  </si>
-  <si>
-    <t>اكياس بانيه s.p</t>
-  </si>
-  <si>
-    <t>طبق مسطح 1/2 شفاف</t>
-  </si>
-  <si>
-    <t>طبق مسطح 3/4شفاف</t>
-  </si>
-  <si>
-    <t>كراتين s.p ابيض</t>
-  </si>
-  <si>
-    <t>علب بلاستيك شفاف</t>
-  </si>
-  <si>
-    <t>اكياس كفته 3ك ابوهاشم</t>
-  </si>
-  <si>
-    <t>أكياس استربس الهنا ص</t>
-  </si>
-  <si>
-    <t>اكياس عجينه بقري 5كيلو اسبيشيال</t>
-  </si>
-  <si>
-    <t>اكياس سجق اسبيشيال كيلو5</t>
-  </si>
-  <si>
-    <t>اكياس عرض نايلون(60*90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">كراتين الهنا ازرق </t>
-  </si>
-  <si>
-    <t xml:space="preserve">كراتين الهنا اخضر </t>
-  </si>
-  <si>
-    <t>كراتين اسبشيال احمر</t>
-  </si>
-  <si>
-    <t>كراتين اسبشيال اسود</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مذيب </t>
-  </si>
-  <si>
-    <t>اكياس 40 * 60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">برانيك صويا </t>
-  </si>
-  <si>
-    <t>برنيك برجر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">برنيك سجق </t>
-  </si>
-  <si>
-    <t>ممبار</t>
-  </si>
-  <si>
-    <t>خام عجينة سجق أبو هاشم</t>
-  </si>
-  <si>
-    <t>خام عجينة كفته أبو هاشم</t>
-  </si>
-  <si>
-    <t>خام عجينة برجر  أبو هاشم</t>
-  </si>
-  <si>
-    <t>خام مفروم صافى 5ك</t>
-  </si>
-  <si>
-    <t>خام عجينة برجر  اسبيشيال</t>
-  </si>
-  <si>
-    <t>خاج عجينة كفته اسبيشيال</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خام مفروم اسبيشيال </t>
-  </si>
-  <si>
-    <t xml:space="preserve">خام عجينه بقري اسبيشيال </t>
-  </si>
-  <si>
-    <t xml:space="preserve">خام عجينه مفروم صويا </t>
-  </si>
-  <si>
-    <t>خام عجينه سجق اسبيشيال</t>
-  </si>
-  <si>
-    <t>خام مفروم صويا الهنا</t>
-  </si>
-  <si>
-    <t>خام عجينة برجر  الهنا</t>
-  </si>
-  <si>
-    <t>خام عجينة كفته الهنا</t>
-  </si>
-  <si>
-    <t>خام عجينة سجق الهنا</t>
-  </si>
-  <si>
-    <t>فلاتر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">استطوانة فريون </t>
+    <t>طبق مسطح 1 ك شفاف</t>
+  </si>
+  <si>
+    <t>أكياس استربس وبانيه شفاف ص</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أكياس بانيه استربس 5 الهنا </t>
+  </si>
+  <si>
+    <t xml:space="preserve">أكياس استربس اسبيشيال ص </t>
+  </si>
+  <si>
+    <t>خام عجينة برجر الهنا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">موزة فرخة </t>
   </si>
   <si>
     <t xml:space="preserve">فلتر خاص بالثلاجة </t>
   </si>
   <si>
-    <t xml:space="preserve">زيت سيارات </t>
-  </si>
-  <si>
-    <t>اسم الصنف</t>
-  </si>
-  <si>
-    <t>الرصيد النهائي المصنع</t>
-  </si>
-  <si>
-    <t>الرصيد النهائي النهضه</t>
-  </si>
-  <si>
-    <t>الرصيد النهائي المنوفية</t>
-  </si>
-  <si>
-    <t>الرصيد النهائي التغليف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بصل </t>
-  </si>
-  <si>
-    <t>ثوم</t>
-  </si>
-  <si>
-    <t>فلفل بارد</t>
-  </si>
-  <si>
-    <t>مفروم فراخ شعبي</t>
-  </si>
-  <si>
-    <t>صميد</t>
-  </si>
-  <si>
-    <t>صويا لحمه</t>
-  </si>
-  <si>
-    <t>صويا اوزيليت</t>
-  </si>
-  <si>
-    <t>مفروم فراخ فاخر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دهن بلدي </t>
-  </si>
-  <si>
-    <t>لحم كتف</t>
-  </si>
-  <si>
-    <t>لحم رقبه</t>
-  </si>
-  <si>
-    <t>لحم سن</t>
-  </si>
-  <si>
-    <t>لحمه ارباع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سمانة هندي </t>
-  </si>
-  <si>
-    <t>فلانك</t>
-  </si>
-  <si>
-    <t>برغل</t>
-  </si>
-  <si>
-    <t>صويا  فراخ</t>
-  </si>
-  <si>
-    <t>كبده</t>
-  </si>
-  <si>
-    <t>جلد</t>
-  </si>
-  <si>
-    <t>هانك</t>
-  </si>
-  <si>
-    <t>دوبريه</t>
-  </si>
-  <si>
-    <t>فلفل رومي حامي</t>
-  </si>
-  <si>
-    <t>بقسماط اصفر</t>
-  </si>
-  <si>
-    <t>بقسماط ابيض</t>
-  </si>
-  <si>
-    <t>بطاطس</t>
-  </si>
-  <si>
-    <t>دوبرية بسطرمة (لحمة)</t>
-  </si>
-  <si>
-    <t>قلب برازيلي</t>
-  </si>
-  <si>
-    <t>بوش</t>
-  </si>
-  <si>
-    <t>شعريه</t>
-  </si>
-  <si>
-    <t>دقيق</t>
-  </si>
-  <si>
-    <t>نشا</t>
-  </si>
-  <si>
-    <t>فلفل اسود</t>
-  </si>
-  <si>
-    <t xml:space="preserve">قرنفل </t>
-  </si>
-  <si>
-    <t xml:space="preserve">كمون </t>
-  </si>
-  <si>
-    <t>كبابه</t>
-  </si>
-  <si>
-    <t>بقدونس</t>
-  </si>
-  <si>
-    <t>لورا</t>
-  </si>
-  <si>
-    <t>خلنجان</t>
-  </si>
-  <si>
-    <t>كزبره</t>
-  </si>
-  <si>
-    <t>قرفه</t>
-  </si>
-  <si>
-    <t>زعتر</t>
-  </si>
-  <si>
-    <t>شطه</t>
-  </si>
-  <si>
-    <t>جوزه الطيب</t>
-  </si>
-  <si>
-    <t>ينسون</t>
-  </si>
-  <si>
-    <t>حبهان</t>
-  </si>
-  <si>
-    <t>بابريكا</t>
-  </si>
-  <si>
-    <t>جنزبيل</t>
-  </si>
-  <si>
-    <t>الملح</t>
-  </si>
-  <si>
-    <t>فوسفات</t>
-  </si>
-  <si>
-    <t>جلتومات</t>
-  </si>
-  <si>
-    <t>طعم سجق بودر</t>
-  </si>
-  <si>
-    <t>طعم ليه</t>
-  </si>
-  <si>
-    <t>طعم كفته</t>
-  </si>
-  <si>
-    <t>طعم برجر</t>
-  </si>
-  <si>
-    <t>طعم بيف</t>
-  </si>
-  <si>
-    <t>طعم شواي</t>
-  </si>
-  <si>
-    <t>طعم دخان</t>
-  </si>
-  <si>
-    <t>سكر</t>
-  </si>
-  <si>
-    <t>فلفل ابيض</t>
-  </si>
-  <si>
-    <t>لون طبيعي</t>
-  </si>
-  <si>
-    <t>طعم فراخ</t>
-  </si>
-  <si>
-    <t>زيوت بسطرمه</t>
-  </si>
-  <si>
-    <t>ثوم بودر</t>
-  </si>
-  <si>
-    <t>كامينا</t>
-  </si>
-  <si>
-    <t>MX</t>
-  </si>
-  <si>
-    <t>زيت سجق</t>
-  </si>
-  <si>
-    <t>كمينا ابيض</t>
-  </si>
-  <si>
-    <t>كروت كبده شرائح 350</t>
-  </si>
-  <si>
-    <t>اكياس افيز</t>
-  </si>
-  <si>
-    <t>لازق</t>
-  </si>
-  <si>
-    <t>كراتين ابوهاشم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ورق برجر </t>
-  </si>
-  <si>
-    <t xml:space="preserve">مزيل لماكينة التغليف </t>
-  </si>
-  <si>
-    <t>الإجمالي</t>
-  </si>
-  <si>
-    <t>مفروم ابو هاشم 350</t>
-  </si>
-  <si>
-    <t>مفروم صافي ابوهاشم 500</t>
-  </si>
-  <si>
-    <t>كبده اسكندراني 370</t>
-  </si>
-  <si>
-    <t>سجق ابوهاشم 3ك</t>
-  </si>
-  <si>
-    <t>سجق ابوهاشم 1ك</t>
-  </si>
-  <si>
-    <t>سجق ابوهاشم 800</t>
-  </si>
-  <si>
-    <t>سجق ابوهاشم 350</t>
-  </si>
-  <si>
-    <t>كفته ابوهاشم 800</t>
-  </si>
-  <si>
-    <t>كفته ابوهاشم 350</t>
-  </si>
-  <si>
-    <t>برجر ابوهاشم 1.5</t>
-  </si>
-  <si>
-    <t>برجر ابوهاشم1100</t>
-  </si>
-  <si>
-    <t>برجر ابو هاشم 800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">برجر ابوهاشم 600 </t>
-  </si>
-  <si>
-    <t>برجر ابوهاشم 400</t>
-  </si>
-  <si>
-    <t>شاورما  400</t>
-  </si>
-  <si>
-    <t>بفتيك 400</t>
-  </si>
-  <si>
-    <t>قطع  400</t>
-  </si>
-  <si>
-    <t>قطع 800</t>
-  </si>
-  <si>
-    <t>مفروم ابو هاشم 3 ك</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سجق ابو هاشم 2 ك </t>
-  </si>
-  <si>
-    <t xml:space="preserve">كبده امريكي3 ك </t>
-  </si>
-  <si>
-    <t>مفروم صويا-بروتين  400 ش</t>
-  </si>
-  <si>
-    <t>مفروم صويا-بروتين 400 علب</t>
-  </si>
-  <si>
-    <t>برجر ابوهاشم 1200</t>
-  </si>
-  <si>
-    <t>كبده اك</t>
-  </si>
-  <si>
-    <t>برجر ابوهاشم 1000</t>
-  </si>
-  <si>
-    <t>عجينة سجق ابوهاشم 1ك</t>
-  </si>
-  <si>
-    <t>عجينة كفته ابو هاشم 5 ك</t>
-  </si>
-  <si>
-    <t>كفتة ابو هاشم 1ك</t>
-  </si>
-  <si>
-    <t>كيس كبده 3 ك برازيلي</t>
-  </si>
-  <si>
-    <t>سجق ابو هاشم 1.5 ك</t>
-  </si>
-  <si>
-    <t>عجينة سجق ابوهاشم 3ك</t>
-  </si>
-  <si>
-    <t>كبده  500</t>
-  </si>
-  <si>
-    <t>سجق الهنا 700</t>
-  </si>
-  <si>
-    <t>سجق الهنا 300</t>
-  </si>
-  <si>
-    <t>كفته الهنا 800</t>
-  </si>
-  <si>
-    <t>كفته الهنا 350</t>
-  </si>
-  <si>
-    <t>برجر الهنا 800</t>
-  </si>
-  <si>
-    <t>برجر الهنا 900</t>
-  </si>
-  <si>
-    <t>برجر الهنا 350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سجق الهنا 3 ك </t>
-  </si>
-  <si>
-    <t xml:space="preserve">سجق الهنا 5 ك </t>
-  </si>
-  <si>
-    <t xml:space="preserve">بانيه 700 </t>
-  </si>
-  <si>
-    <t>بانيه 800</t>
-  </si>
-  <si>
-    <t>بانيه 900</t>
-  </si>
-  <si>
-    <t>عجينه سجق هنا 5ك</t>
-  </si>
-  <si>
-    <t>سجق الهنا عرض 200ج</t>
-  </si>
-  <si>
-    <t>برجر الهنا عرض 300ج</t>
-  </si>
-  <si>
-    <t>كفتة الهنا عرض 200ج</t>
-  </si>
-  <si>
-    <t>عرض ثلاثي الهنا&lt;سجق برجر كفته &gt;</t>
-  </si>
-  <si>
-    <t>برجر اسبيشيال1ك</t>
-  </si>
-  <si>
-    <t>برجر اسبيشيال 400</t>
-  </si>
-  <si>
-    <t>كفته اسبيشيال 900</t>
-  </si>
-  <si>
-    <t>كفته اسبيشيال 350</t>
-  </si>
-  <si>
-    <t>سجق اسبيشيال 700</t>
-  </si>
-  <si>
-    <t>سجق اسبيشيال300</t>
-  </si>
-  <si>
-    <t>بانيه اسبيشيال900</t>
-  </si>
-  <si>
-    <t>بانيه اسبيشيال 800</t>
-  </si>
-  <si>
-    <t>بانيه اسبيشيال حار800</t>
-  </si>
-  <si>
-    <t>سجق اسبشيال 5ك</t>
-  </si>
-  <si>
-    <t>مفروم اسبيشيال 400</t>
-  </si>
-  <si>
-    <t>عجينه بقري اسبيشيال 5 كيلو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عجينه مفروم صويا </t>
-  </si>
-  <si>
-    <t>كبده اسبيشيال 400</t>
-  </si>
-  <si>
-    <t>برجر مخصوص</t>
-  </si>
-  <si>
-    <t>كفتة مخصوص</t>
-  </si>
-  <si>
-    <t>سجق مخصوص 1ك</t>
-  </si>
-  <si>
-    <t>عرض ثلاثي &lt;سجق برجر كفته 700جرام&gt;</t>
-  </si>
-  <si>
-    <t>عجينه بقري اسبيشيال 500جرام</t>
-  </si>
-  <si>
-    <t>بانيه 5كيلو حار</t>
-  </si>
-  <si>
-    <t>عجينة بقرى 250ج</t>
-  </si>
-  <si>
-    <t>مفروم صافى 5ك</t>
-  </si>
-  <si>
-    <t>موزة فرخة</t>
-  </si>
-  <si>
-    <t>بانيه بارد دوفا</t>
-  </si>
-  <si>
-    <t>لحمة قطع كيلو أبو هاشم</t>
-  </si>
-  <si>
-    <t>كبده اسبيشيال 3 ك</t>
-  </si>
-  <si>
-    <t>بفتيك 600</t>
-  </si>
-  <si>
-    <t>عجينة كفته الهنا الـ5 ك</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عجينة بقري 1 ك </t>
-  </si>
-  <si>
-    <t xml:space="preserve">عجينة بقري 3 ك </t>
-  </si>
-  <si>
-    <t>النفق</t>
-  </si>
-  <si>
-    <t>فيليه</t>
-  </si>
-  <si>
-    <t>كرفس</t>
-  </si>
-  <si>
-    <t>روزماري</t>
-  </si>
-  <si>
-    <t>بصل بودر</t>
-  </si>
-  <si>
-    <t>كربوناتو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شرش بودر </t>
-  </si>
-  <si>
-    <t>أكياس بانيه الهنا 5 ك</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حشوة زيت </t>
-  </si>
-  <si>
-    <t>استبربس SP 900</t>
-  </si>
-  <si>
-    <t>استبربس 800</t>
-  </si>
-  <si>
-    <t>استبربس GB 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خام عجينة برجر اسبيشيال </t>
-  </si>
-  <si>
-    <t>أكياس استربس اسبيشيال ص</t>
-  </si>
-  <si>
-    <t>بانيه 1 ك</t>
-  </si>
-  <si>
-    <t xml:space="preserve">كفته أبو هاشم 1 ك </t>
-  </si>
-  <si>
-    <t xml:space="preserve">فلتر هواء </t>
-  </si>
-  <si>
-    <t>استربس 1 ك</t>
-  </si>
-  <si>
-    <t>جرد شهر 8 لعام 2026</t>
+    <t>فلتر هواء دبابة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ماجي </t>
+  </si>
+  <si>
+    <t>خلطة استربس 10</t>
+  </si>
+  <si>
+    <t>خلطة استربس 20</t>
+  </si>
+  <si>
+    <t>خلطة استربس 30</t>
+  </si>
+  <si>
+    <t>خلطة بانيه A</t>
+  </si>
+  <si>
+    <t>خلطة بانيه B</t>
   </si>
 </sst>
 </file>
@@ -1093,7 +1120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1187,21 +1214,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1399,24 +1411,24 @@
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1430,8 +1442,8 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1440,9 +1452,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="3" xr:uid="{98BF7EF2-0FB0-4F53-BF07-4F0204879330}"/>
@@ -1800,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69590074-F9E1-47CB-9D65-9D1D53B05140}">
-  <dimension ref="A2:I152"/>
+  <dimension ref="A2:I169"/>
   <sheetFormatPr defaultColWidth="9.19140625" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.671875" style="1" bestFit="1" customWidth="1"/>
@@ -1817,43 +1831,43 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="D2" s="9" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:9" ht="18.75" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B5" s="11">
         <v>500</v>
@@ -1868,12 +1882,12 @@
       <c r="F5" s="11">
         <v>0</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="17">
         <f t="shared" ref="G5:G36" si="0">SUM(B5:F5)</f>
         <v>500</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I5" s="5">
         <v>92</v>
@@ -1881,10 +1895,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B6" s="11">
-        <v>1240.25</v>
+        <v>1240</v>
       </c>
       <c r="C6" s="11">
         <v>9.3000000000000007</v>
@@ -1900,10 +1914,10 @@
       </c>
       <c r="G6" s="11">
         <f t="shared" si="0"/>
-        <v>1249.55</v>
+        <v>1249.3</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I6" s="5">
         <v>30</v>
@@ -1911,7 +1925,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B7" s="11">
         <v>320</v>
@@ -1931,7 +1945,7 @@
         <v>320</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I7" s="5">
         <v>172</v>
@@ -1939,7 +1953,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B8" s="11">
         <v>2110</v>
@@ -1961,7 +1975,7 @@
         <v>2120</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I8" s="5">
         <v>358</v>
@@ -1969,7 +1983,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B9" s="11">
         <v>1241</v>
@@ -1989,7 +2003,7 @@
         <v>1241</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I9" s="5">
         <v>0</v>
@@ -1997,7 +2011,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B10" s="11">
         <v>680</v>
@@ -2019,7 +2033,7 @@
         <v>777</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I10" s="5">
         <v>201</v>
@@ -2027,7 +2041,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B11" s="11">
         <v>151.5</v>
@@ -2047,7 +2061,7 @@
         <v>151.5</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I11" s="5">
         <v>158</v>
@@ -2055,7 +2069,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B12" s="11">
         <v>415</v>
@@ -2075,7 +2089,7 @@
         <v>415</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I12" s="5">
         <v>278</v>
@@ -2083,14 +2097,12 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B13" s="11">
-        <v>1751.1999999999998</v>
-      </c>
-      <c r="C13" s="11">
-        <v>3.65</v>
-      </c>
+        <v>1754.85</v>
+      </c>
+      <c r="C13" s="11"/>
       <c r="D13" s="11">
         <v>0</v>
       </c>
@@ -2105,7 +2117,7 @@
         <v>1754.85</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I13" s="5">
         <v>81</v>
@@ -2113,7 +2125,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B14" s="11">
         <v>20</v>
@@ -2135,7 +2147,7 @@
         <v>40</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I14" s="5">
         <v>147</v>
@@ -2143,7 +2155,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B15" s="11">
         <v>40</v>
@@ -2165,7 +2177,7 @@
         <v>60</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I15" s="5">
         <v>240</v>
@@ -2173,7 +2185,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B16" s="11">
         <v>0</v>
@@ -2195,7 +2207,7 @@
         <v>20</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
@@ -2203,7 +2215,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B17" s="11">
         <v>5</v>
@@ -2225,7 +2237,7 @@
         <v>25</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I17" s="5">
         <v>0</v>
@@ -2233,7 +2245,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B18" s="11">
         <v>0</v>
@@ -2253,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I18" s="5">
         <v>0</v>
@@ -2261,7 +2273,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
-        <v>93</v>
+        <v>243</v>
       </c>
       <c r="B19" s="11">
         <v>106</v>
@@ -2283,7 +2295,7 @@
         <v>110</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="I19" s="5">
         <v>0</v>
@@ -2291,7 +2303,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B20" s="11">
         <v>3090</v>
@@ -2313,7 +2325,7 @@
         <v>3325</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
@@ -2321,7 +2333,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B21" s="11">
         <v>180</v>
@@ -2341,7 +2353,7 @@
         <v>180</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I21" s="5">
         <v>4200</v>
@@ -2349,7 +2361,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B22" s="11">
         <v>63.30400000000003</v>
@@ -2369,7 +2381,7 @@
         <v>63.30400000000003</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
@@ -2377,7 +2389,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B23" s="11">
         <v>359</v>
@@ -2397,7 +2409,7 @@
         <v>359</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
@@ -2405,7 +2417,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B24" s="11">
         <v>118</v>
@@ -2425,7 +2437,7 @@
         <v>118</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I24" s="5">
         <v>0</v>
@@ -2433,7 +2445,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B25" s="11">
         <v>470</v>
@@ -2453,7 +2465,7 @@
         <v>470</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
@@ -2461,7 +2473,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B26" s="11">
         <v>15.7</v>
@@ -2481,7 +2493,7 @@
         <v>15.7</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
@@ -2489,7 +2501,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B27" s="11">
         <v>0</v>
@@ -2509,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I27" s="5">
         <v>36</v>
@@ -2517,7 +2529,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B28" s="11">
         <v>0</v>
@@ -2537,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
@@ -2545,7 +2557,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B29" s="11">
         <v>0</v>
@@ -2565,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
@@ -2573,7 +2585,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B30" s="11">
         <v>0</v>
@@ -2593,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I30" s="5">
         <v>89</v>
@@ -2601,7 +2613,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B31" s="11">
         <v>0</v>
@@ -2621,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I31" s="5">
         <v>0</v>
@@ -2629,7 +2641,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B32" s="11">
         <v>0</v>
@@ -2649,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I32" s="5">
         <v>0</v>
@@ -2657,7 +2669,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B33" s="11">
         <v>0</v>
@@ -2677,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I33" s="5">
         <v>0</v>
@@ -2685,7 +2697,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B34" s="11">
         <v>0</v>
@@ -2705,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I34" s="5">
         <v>0</v>
@@ -2713,7 +2725,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B35" s="11">
         <v>0</v>
@@ -2733,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I35" s="5">
         <v>0</v>
@@ -2741,7 +2753,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B36" s="11">
         <v>400</v>
@@ -2761,7 +2773,7 @@
         <v>400</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I36" s="5">
         <v>0</v>
@@ -2769,7 +2781,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B37" s="11">
         <v>36.379999999999995</v>
@@ -2789,7 +2801,7 @@
         <v>36.379999999999995</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="I37" s="5">
         <v>0</v>
@@ -2797,7 +2809,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B38" s="11">
         <v>5.0999999999999996</v>
@@ -2817,7 +2829,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I38" s="5">
         <v>0</v>
@@ -2825,7 +2837,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B39" s="11">
         <v>14.9</v>
@@ -2845,7 +2857,7 @@
         <v>14.9</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="I39" s="5">
         <v>247</v>
@@ -2853,7 +2865,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B40" s="11">
         <v>0</v>
@@ -2873,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I40" s="5">
         <v>1009</v>
@@ -2881,7 +2893,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="10" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B41" s="11">
         <v>10.6</v>
@@ -2901,7 +2913,7 @@
         <v>10.6</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="I41" s="5">
         <v>1043</v>
@@ -2909,7 +2921,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B42" s="11">
         <v>10</v>
@@ -2929,7 +2941,7 @@
         <v>10</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="I42" s="5">
         <v>1885</v>
@@ -2937,7 +2949,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B43" s="11">
         <v>12.5</v>
@@ -2957,7 +2969,7 @@
         <v>12.5</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I43" s="5">
         <v>60</v>
@@ -2965,7 +2977,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B44" s="11">
         <v>4.9749999999999996</v>
@@ -2985,7 +2997,7 @@
         <v>4.9749999999999996</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I44" s="5">
         <v>680</v>
@@ -2993,7 +3005,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B45" s="11">
         <v>55</v>
@@ -3013,7 +3025,7 @@
         <v>55</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="I45" s="5">
         <v>1051</v>
@@ -3021,7 +3033,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B46" s="11">
         <v>23.7</v>
@@ -3041,7 +3053,7 @@
         <v>23.7</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I46" s="5">
         <v>0</v>
@@ -3049,7 +3061,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B47" s="11">
         <v>3</v>
@@ -3069,7 +3081,7 @@
         <v>3</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I47" s="5">
         <v>121</v>
@@ -3077,7 +3089,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B48" s="11">
         <v>63</v>
@@ -3097,7 +3109,7 @@
         <v>63</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I48" s="5">
         <v>0</v>
@@ -3105,7 +3117,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B49" s="11">
         <v>1.7899999999999998</v>
@@ -3125,7 +3137,7 @@
         <v>1.7899999999999998</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I49" s="5">
         <v>483</v>
@@ -3133,7 +3145,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B50" s="11">
         <v>10.44</v>
@@ -3153,7 +3165,7 @@
         <v>10.44</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I50" s="5">
         <v>0</v>
@@ -3161,7 +3173,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B51" s="11">
         <v>9.1999999999999993</v>
@@ -3181,7 +3193,7 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="I51" s="5">
         <v>0</v>
@@ -3189,7 +3201,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="10" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B52" s="11">
         <v>0</v>
@@ -3209,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="I52" s="5">
         <v>0</v>
@@ -3217,7 +3229,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B53" s="11">
         <v>31.700000000000003</v>
@@ -3237,7 +3249,7 @@
         <v>31.700000000000003</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I53" s="5">
         <v>0</v>
@@ -3245,7 +3257,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B54" s="11">
         <v>9.5</v>
@@ -3265,7 +3277,7 @@
         <v>9.5</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="I54" s="5">
         <v>0</v>
@@ -3273,7 +3285,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B55" s="11">
         <v>742</v>
@@ -3293,7 +3305,7 @@
         <v>742</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="I55" s="5">
         <v>14</v>
@@ -3301,7 +3313,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="10" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B56" s="11">
         <v>212</v>
@@ -3321,7 +3333,7 @@
         <v>212</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="I56" s="5">
         <v>0</v>
@@ -3329,7 +3341,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B57" s="11">
         <v>127.5</v>
@@ -3349,7 +3361,7 @@
         <v>127.5</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="I57" s="5">
         <v>868</v>
@@ -3357,7 +3369,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B58" s="11">
         <v>5.25</v>
@@ -3377,7 +3389,7 @@
         <v>5.25</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I58" s="5">
         <v>626</v>
@@ -3385,7 +3397,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="10" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B59" s="11">
         <v>0</v>
@@ -3405,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I59" s="5">
         <v>876</v>
@@ -3413,7 +3425,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="10" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B60" s="11">
         <v>19.305</v>
@@ -3433,7 +3445,7 @@
         <v>19.305</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="I60" s="6">
         <v>1155</v>
@@ -3441,7 +3453,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="10" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B61" s="11">
         <v>31.5</v>
@@ -3461,7 +3473,7 @@
         <v>31.5</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="I61" s="5">
         <v>68</v>
@@ -3469,7 +3481,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="10" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B62" s="11">
         <v>7.2</v>
@@ -3489,7 +3501,7 @@
         <v>7.2</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I62" s="5">
         <v>22</v>
@@ -3497,7 +3509,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="10" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B63" s="11">
         <v>9.5</v>
@@ -3517,7 +3529,7 @@
         <v>9.5</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="I63" s="5">
         <v>36</v>
@@ -3525,7 +3537,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="10" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B64" s="11">
         <v>17.5</v>
@@ -3545,7 +3557,7 @@
         <v>17.5</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="I64" s="5">
         <v>0</v>
@@ -3553,7 +3565,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B65" s="11">
         <v>0</v>
@@ -3573,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="I65" s="5">
         <v>0</v>
@@ -3581,7 +3593,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="10" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B66" s="11">
         <v>1.35</v>
@@ -3601,7 +3613,7 @@
         <v>1.35</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="I66" s="5">
         <v>0</v>
@@ -3609,7 +3621,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="10" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B67" s="11">
         <v>21.95</v>
@@ -3629,7 +3641,7 @@
         <v>21.95</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="I67" s="5">
         <v>0</v>
@@ -3637,7 +3649,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="10" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B68" s="11">
         <v>3.4949999999999997</v>
@@ -3657,7 +3669,7 @@
         <v>3.4949999999999997</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I68" s="5">
         <v>0</v>
@@ -3665,7 +3677,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B69" s="11">
         <v>0</v>
@@ -3685,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="I69" s="5">
         <v>14</v>
@@ -3693,7 +3705,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="10" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B70" s="11">
         <v>10.664999999999999</v>
@@ -3713,7 +3725,7 @@
         <v>10.664999999999999</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="I70" s="5">
         <v>0</v>
@@ -3721,7 +3733,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="10" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B71" s="11">
         <v>0</v>
@@ -3741,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="I71" s="5">
         <v>0</v>
@@ -3749,7 +3761,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="10" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B72" s="11">
         <v>6</v>
@@ -3769,7 +3781,7 @@
         <v>6</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="I72" s="5">
         <v>0</v>
@@ -3777,7 +3789,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="10" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B73" s="11">
         <v>0</v>
@@ -3797,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I73" s="5">
         <v>0</v>
@@ -3805,7 +3817,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="10" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B74" s="11">
         <v>4.33</v>
@@ -3825,7 +3837,7 @@
         <v>4.33</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I74" s="5">
         <v>0</v>
@@ -3833,7 +3845,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B75" s="11">
         <v>34.6</v>
@@ -3853,7 +3865,7 @@
         <v>34.6</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I75" s="5">
         <v>0</v>
@@ -3861,7 +3873,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="10" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B76" s="11">
         <v>2.3999999999999995</v>
@@ -3881,7 +3893,7 @@
         <v>2.3999999999999995</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="I76" s="5">
         <v>0</v>
@@ -3889,7 +3901,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="10" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B77" s="11">
         <v>18</v>
@@ -3909,7 +3921,7 @@
         <v>18</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="I77" s="5">
         <v>0</v>
@@ -3917,7 +3929,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="10" t="s">
-        <v>146</v>
+        <v>244</v>
       </c>
       <c r="B78" s="11">
         <v>0</v>
@@ -3937,7 +3949,7 @@
         <v>14451</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="I78" s="5">
         <v>0</v>
@@ -3945,7 +3957,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="10" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B79" s="11">
         <v>700</v>
@@ -3965,7 +3977,7 @@
         <v>731</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="I79" s="5">
         <v>0</v>
@@ -3973,7 +3985,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="10" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B80" s="11">
         <v>28</v>
@@ -3993,7 +4005,7 @@
         <v>67</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="I80" s="5">
         <v>0</v>
@@ -4001,7 +4013,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="10" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B81" s="11">
         <v>0</v>
@@ -4021,7 +4033,7 @@
         <v>754</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I81" s="5">
         <v>0</v>
@@ -4029,7 +4041,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="10" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B82" s="11">
         <v>484</v>
@@ -4049,7 +4061,7 @@
         <v>489</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I82" s="5">
         <v>0</v>
@@ -4057,7 +4069,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="10" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B83" s="11">
         <v>1</v>
@@ -4077,7 +4089,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I83" s="5">
         <v>0</v>
@@ -4100,12 +4112,12 @@
       <c r="F84" s="11">
         <v>46</v>
       </c>
-      <c r="G84" s="11">
+      <c r="G84" s="15">
         <f t="shared" si="2"/>
         <v>708.5</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I84" s="5">
         <v>0</v>
@@ -4128,12 +4140,12 @@
       <c r="F85" s="11">
         <v>9.5</v>
       </c>
-      <c r="G85" s="11">
+      <c r="G85" s="15">
         <f t="shared" si="2"/>
         <v>568.79999999999995</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I85" s="5">
         <v>0</v>
@@ -4156,12 +4168,12 @@
       <c r="F86" s="11">
         <v>37</v>
       </c>
-      <c r="G86" s="11">
+      <c r="G86" s="15">
         <f t="shared" si="2"/>
         <v>359.5</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I86" s="5">
         <v>0</v>
@@ -4184,12 +4196,12 @@
       <c r="F87" s="11">
         <v>30</v>
       </c>
-      <c r="G87" s="11">
+      <c r="G87" s="15">
         <f t="shared" si="2"/>
         <v>470</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I87" s="5">
         <v>0</v>
@@ -4212,12 +4224,12 @@
       <c r="F88" s="11">
         <v>0</v>
       </c>
-      <c r="G88" s="11">
+      <c r="G88" s="15">
         <f t="shared" si="2"/>
         <v>45.6</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I88" s="5">
         <v>0</v>
@@ -4240,12 +4252,12 @@
       <c r="F89" s="11">
         <v>24</v>
       </c>
-      <c r="G89" s="11">
+      <c r="G89" s="15">
         <f t="shared" si="2"/>
         <v>494.7</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I89" s="5">
         <v>0</v>
@@ -4268,12 +4280,12 @@
       <c r="F90" s="11">
         <v>10.5</v>
       </c>
-      <c r="G90" s="11">
+      <c r="G90" s="15">
         <f t="shared" si="2"/>
         <v>293</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I90" s="5">
         <v>0</v>
@@ -4296,12 +4308,12 @@
       <c r="F91" s="11">
         <v>13</v>
       </c>
-      <c r="G91" s="11">
+      <c r="G91" s="15">
         <f t="shared" si="2"/>
         <v>373</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I91" s="5">
         <v>0</v>
@@ -4324,12 +4336,12 @@
       <c r="F92" s="11">
         <v>7</v>
       </c>
-      <c r="G92" s="11">
+      <c r="G92" s="15">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I92" s="5">
         <v>0</v>
@@ -4352,12 +4364,12 @@
       <c r="F93" s="11">
         <v>0</v>
       </c>
-      <c r="G93" s="11">
+      <c r="G93" s="15">
         <f t="shared" si="2"/>
         <v>4.8499999999999996</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I93" s="5">
         <v>0</v>
@@ -4380,12 +4392,12 @@
       <c r="F94" s="11">
         <v>23</v>
       </c>
-      <c r="G94" s="11">
+      <c r="G94" s="15">
         <f t="shared" si="2"/>
         <v>88.8</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I94" s="5">
         <v>0</v>
@@ -4408,12 +4420,12 @@
       <c r="F95" s="11">
         <v>0</v>
       </c>
-      <c r="G95" s="11">
+      <c r="G95" s="15">
         <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I95" s="5">
         <v>0</v>
@@ -4436,12 +4448,12 @@
       <c r="F96" s="11">
         <v>0</v>
       </c>
-      <c r="G96" s="11">
+      <c r="G96" s="15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="I96" s="5">
         <v>3</v>
@@ -4464,12 +4476,12 @@
       <c r="F97" s="11">
         <v>27</v>
       </c>
-      <c r="G97" s="11">
+      <c r="G97" s="15">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I97" s="5">
         <v>0</v>
@@ -4492,12 +4504,12 @@
       <c r="F98" s="11">
         <v>14.633000000000001</v>
       </c>
-      <c r="G98" s="11">
+      <c r="G98" s="15">
         <f t="shared" si="2"/>
         <v>35.933</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="I98" s="5">
         <v>0</v>
@@ -4520,12 +4532,12 @@
       <c r="F99" s="11">
         <v>5.29</v>
       </c>
-      <c r="G99" s="11">
+      <c r="G99" s="15">
         <f t="shared" si="2"/>
         <v>5.29</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="I99" s="5">
         <v>0</v>
@@ -4548,12 +4560,12 @@
       <c r="F100" s="11">
         <v>140.47400000000005</v>
       </c>
-      <c r="G100" s="11">
+      <c r="G100" s="15">
         <f t="shared" si="2"/>
         <v>140.47400000000005</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="I100" s="5">
         <v>0</v>
@@ -4576,12 +4588,12 @@
       <c r="F101" s="11">
         <v>200</v>
       </c>
-      <c r="G101" s="11">
+      <c r="G101" s="15">
         <f t="shared" ref="G101:G130" si="3">SUM(B101:F101)</f>
         <v>44700</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="I101" s="5">
         <v>0</v>
@@ -4604,12 +4616,12 @@
       <c r="F102" s="11">
         <v>1200</v>
       </c>
-      <c r="G102" s="11">
+      <c r="G102" s="15">
         <f t="shared" si="3"/>
         <v>21200</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="I102" s="5">
         <v>0</v>
@@ -4632,12 +4644,12 @@
       <c r="F103" s="11">
         <v>0</v>
       </c>
-      <c r="G103" s="11">
+      <c r="G103" s="15">
         <f t="shared" si="3"/>
         <v>260</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="I103" s="5">
         <v>12</v>
@@ -4660,12 +4672,12 @@
       <c r="F104" s="11">
         <v>18.600000000000001</v>
       </c>
-      <c r="G104" s="11">
+      <c r="G104" s="15">
         <f t="shared" si="3"/>
         <v>68.599999999999994</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="I104" s="5">
         <v>1091</v>
@@ -4688,12 +4700,12 @@
       <c r="F105" s="11">
         <v>0</v>
       </c>
-      <c r="G105" s="11">
+      <c r="G105" s="15">
         <f t="shared" si="3"/>
         <v>51.900000000000006</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="I105" s="5">
         <v>1090</v>
@@ -4716,7 +4728,7 @@
       <c r="F106" s="11">
         <v>0</v>
       </c>
-      <c r="G106" s="11">
+      <c r="G106" s="15">
         <f t="shared" si="3"/>
         <v>48.650000000000006</v>
       </c>
@@ -4742,7 +4754,7 @@
       <c r="F107" s="11">
         <v>10.4</v>
       </c>
-      <c r="G107" s="11">
+      <c r="G107" s="15">
         <f t="shared" si="3"/>
         <v>21.3</v>
       </c>
@@ -4753,7 +4765,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="10" t="s">
-        <v>24</v>
+        <v>245</v>
       </c>
       <c r="B108" s="11">
         <v>0</v>
@@ -4768,7 +4780,7 @@
       <c r="F108" s="11">
         <v>2000</v>
       </c>
-      <c r="G108" s="11">
+      <c r="G108" s="15">
         <f t="shared" si="3"/>
         <v>2000</v>
       </c>
@@ -4779,7 +4791,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B109" s="11">
         <v>0</v>
@@ -4794,7 +4806,7 @@
       <c r="F109" s="11">
         <v>9225</v>
       </c>
-      <c r="G109" s="11">
+      <c r="G109" s="15">
         <f t="shared" si="3"/>
         <v>9225</v>
       </c>
@@ -4805,7 +4817,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B110" s="11">
         <v>0</v>
@@ -4820,7 +4832,7 @@
       <c r="F110" s="11">
         <v>8786</v>
       </c>
-      <c r="G110" s="11">
+      <c r="G110" s="15">
         <f t="shared" si="3"/>
         <v>8786</v>
       </c>
@@ -4831,7 +4843,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B111" s="11">
         <v>81.5</v>
@@ -4846,7 +4858,7 @@
       <c r="F111" s="11">
         <v>26</v>
       </c>
-      <c r="G111" s="11">
+      <c r="G111" s="15">
         <f t="shared" si="3"/>
         <v>583.5</v>
       </c>
@@ -4857,7 +4869,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B112" s="11">
         <v>0</v>
@@ -4872,7 +4884,7 @@
       <c r="F112" s="11">
         <v>13.8</v>
       </c>
-      <c r="G112" s="11">
+      <c r="G112" s="15">
         <f t="shared" si="3"/>
         <v>13.8</v>
       </c>
@@ -4883,14 +4895,14 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="10" t="s">
-        <v>29</v>
+        <v>242</v>
       </c>
       <c r="B113" s="11">
         <v>0</v>
       </c>
       <c r="C113" s="11"/>
       <c r="D113" s="11">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E113" s="11">
         <v>0</v>
@@ -4898,9 +4910,9 @@
       <c r="F113" s="11">
         <v>2000</v>
       </c>
-      <c r="G113" s="11">
+      <c r="G113" s="15">
         <f t="shared" si="3"/>
-        <v>2036</v>
+        <v>2000</v>
       </c>
       <c r="H113" s="11">
         <v>0</v>
@@ -4909,24 +4921,24 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="10" t="s">
-        <v>30</v>
+        <v>246</v>
       </c>
       <c r="B114" s="11">
         <v>0</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E114" s="11">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="F114" s="11">
-        <v>6.1280000000000001</v>
-      </c>
-      <c r="G114" s="11">
+        <v>6.13</v>
+      </c>
+      <c r="G114" s="15">
         <f t="shared" si="3"/>
-        <v>146.12799999999999</v>
+        <v>42.13</v>
       </c>
       <c r="H114" s="11">
         <v>0</v>
@@ -4935,7 +4947,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B115" s="11">
         <v>0</v>
@@ -4945,14 +4957,14 @@
         <v>0</v>
       </c>
       <c r="E115" s="11">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="F115" s="11">
         <v>48.3</v>
       </c>
-      <c r="G115" s="11">
+      <c r="G115" s="15">
         <f t="shared" si="3"/>
-        <v>288.3</v>
+        <v>188.3</v>
       </c>
       <c r="H115" s="11">
         <v>0</v>
@@ -4961,24 +4973,24 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B116" s="11">
-        <v>8.3000000000000007</v>
+        <v>0</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11">
         <v>0</v>
       </c>
       <c r="E116" s="11">
-        <v>198.25</v>
+        <v>240</v>
       </c>
       <c r="F116" s="11">
         <v>120</v>
       </c>
-      <c r="G116" s="11">
+      <c r="G116" s="15">
         <f t="shared" si="3"/>
-        <v>326.55</v>
+        <v>360</v>
       </c>
       <c r="H116" s="11">
         <v>0</v>
@@ -4987,24 +4999,24 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B117" s="11">
-        <v>16.600000000000001</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="C117" s="11"/>
       <c r="D117" s="11">
         <v>0</v>
       </c>
       <c r="E117" s="11">
-        <v>421.75</v>
+        <v>198.25</v>
       </c>
       <c r="F117" s="11">
-        <v>53</v>
-      </c>
-      <c r="G117" s="11">
+        <v>53.6</v>
+      </c>
+      <c r="G117" s="15">
         <f t="shared" si="3"/>
-        <v>491.35</v>
+        <v>260.15000000000003</v>
       </c>
       <c r="H117" s="11">
         <v>0</v>
@@ -5013,24 +5025,24 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B118" s="11">
-        <v>30</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11">
         <v>0</v>
       </c>
       <c r="E118" s="11">
-        <v>660</v>
+        <v>421.75</v>
       </c>
       <c r="F118" s="11">
         <v>18</v>
       </c>
-      <c r="G118" s="11">
+      <c r="G118" s="15">
         <f t="shared" si="3"/>
-        <v>708</v>
+        <v>456.35</v>
       </c>
       <c r="H118" s="11">
         <v>0</v>
@@ -5039,7 +5051,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B119" s="11">
         <v>30</v>
@@ -5049,14 +5061,14 @@
         <v>0</v>
       </c>
       <c r="E119" s="11">
-        <v>743.5</v>
+        <v>660</v>
       </c>
       <c r="F119" s="11">
         <v>19</v>
       </c>
-      <c r="G119" s="11">
+      <c r="G119" s="15">
         <f t="shared" si="3"/>
-        <v>792.5</v>
+        <v>709</v>
       </c>
       <c r="H119" s="11">
         <v>0</v>
@@ -5065,24 +5077,24 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B120" s="11">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="C120" s="11"/>
       <c r="D120" s="11">
         <v>0</v>
       </c>
       <c r="E120" s="11">
-        <v>90</v>
+        <v>743.5</v>
       </c>
       <c r="F120" s="11">
         <v>21.8</v>
       </c>
-      <c r="G120" s="11">
+      <c r="G120" s="15">
         <f t="shared" si="3"/>
-        <v>184.8</v>
+        <v>795.3</v>
       </c>
       <c r="H120" s="11">
         <v>0</v>
@@ -5091,24 +5103,24 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B121" s="11">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="C121" s="11"/>
       <c r="D121" s="11">
         <v>0</v>
       </c>
       <c r="E121" s="11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F121" s="11">
         <v>14</v>
       </c>
-      <c r="G121" s="11">
+      <c r="G121" s="15">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>177</v>
       </c>
       <c r="H121" s="11">
         <v>0</v>
@@ -5117,7 +5129,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B122" s="11">
         <v>0</v>
@@ -5132,7 +5144,7 @@
       <c r="F122" s="11">
         <v>827</v>
       </c>
-      <c r="G122" s="11">
+      <c r="G122" s="15">
         <f t="shared" si="3"/>
         <v>827</v>
       </c>
@@ -5143,7 +5155,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="10" t="s">
-        <v>39</v>
+        <v>247</v>
       </c>
       <c r="B123" s="11">
         <v>0</v>
@@ -5156,11 +5168,11 @@
         <v>0</v>
       </c>
       <c r="F123" s="11">
-        <v>0</v>
-      </c>
-      <c r="G123" s="11">
+        <v>379</v>
+      </c>
+      <c r="G123" s="15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="H123" s="11">
         <v>0</v>
@@ -5169,7 +5181,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="10" t="s">
-        <v>40</v>
+        <v>248</v>
       </c>
       <c r="B124" s="11">
         <v>0</v>
@@ -5182,168 +5194,168 @@
         <v>0</v>
       </c>
       <c r="F124" s="11">
+        <v>0</v>
+      </c>
+      <c r="G124" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H124" s="11">
+        <v>0</v>
+      </c>
+      <c r="I124" s="5"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A125" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B125" s="11">
+        <v>0</v>
+      </c>
+      <c r="C125" s="11"/>
+      <c r="D125" s="11">
+        <v>0</v>
+      </c>
+      <c r="E125" s="11">
+        <v>0</v>
+      </c>
+      <c r="F125" s="11">
+        <v>0</v>
+      </c>
+      <c r="G125" s="15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H125" s="11">
+        <v>0</v>
+      </c>
+      <c r="I125" s="5"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A126" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B126" s="11">
+        <v>0</v>
+      </c>
+      <c r="C126" s="11"/>
+      <c r="D126" s="11">
+        <v>0</v>
+      </c>
+      <c r="E126" s="11">
+        <v>0</v>
+      </c>
+      <c r="F126" s="11">
         <v>1073</v>
       </c>
-      <c r="G124" s="11">
+      <c r="G126" s="15">
         <f t="shared" si="3"/>
         <v>1073</v>
       </c>
-      <c r="H124" s="11">
-        <v>0</v>
-      </c>
-      <c r="I124" s="5"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A125" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B125" s="11">
-        <v>0</v>
-      </c>
-      <c r="C125" s="11"/>
-      <c r="D125" s="11">
-        <v>0</v>
-      </c>
-      <c r="E125" s="11">
-        <v>0</v>
-      </c>
-      <c r="F125" s="11">
-        <v>0</v>
-      </c>
-      <c r="G125" s="11">
+      <c r="H126" s="11">
+        <v>0</v>
+      </c>
+      <c r="I126" s="5"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A127" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B127" s="11">
+        <v>0</v>
+      </c>
+      <c r="C127" s="11"/>
+      <c r="D127" s="11">
+        <v>0</v>
+      </c>
+      <c r="E127" s="11">
+        <v>0</v>
+      </c>
+      <c r="F127" s="11">
+        <v>0</v>
+      </c>
+      <c r="G127" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H125" s="11">
-        <v>0</v>
-      </c>
-      <c r="I125" s="5"/>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A126" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B126" s="11">
+      <c r="H127" s="11">
+        <v>0</v>
+      </c>
+      <c r="I127" s="5"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A128" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B128" s="11">
         <v>11.8</v>
       </c>
-      <c r="C126" s="11"/>
-      <c r="D126" s="11">
-        <v>0</v>
-      </c>
-      <c r="E126" s="11">
-        <v>0</v>
-      </c>
-      <c r="F126" s="11">
-        <v>0</v>
-      </c>
-      <c r="G126" s="11">
+      <c r="C128" s="11"/>
+      <c r="D128" s="11">
+        <v>0</v>
+      </c>
+      <c r="E128" s="11">
+        <v>0</v>
+      </c>
+      <c r="F128" s="16">
+        <v>0</v>
+      </c>
+      <c r="G128" s="15">
         <f t="shared" si="3"/>
         <v>11.8</v>
       </c>
-      <c r="H126" s="11">
-        <v>0</v>
-      </c>
-      <c r="I126" s="5"/>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A127" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B127" s="11">
+      <c r="H128" s="11">
+        <v>0</v>
+      </c>
+      <c r="I128" s="5"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A129" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B129" s="11">
         <v>11.25</v>
       </c>
-      <c r="C127" s="11"/>
-      <c r="D127" s="11">
-        <v>0</v>
-      </c>
-      <c r="E127" s="11">
+      <c r="C129" s="11"/>
+      <c r="D129" s="11">
+        <v>0</v>
+      </c>
+      <c r="E129" s="11">
         <v>100</v>
       </c>
-      <c r="F127" s="11">
+      <c r="F129" s="11">
         <v>1.6279999999999999</v>
       </c>
-      <c r="G127" s="11">
+      <c r="G129" s="11">
         <f t="shared" si="3"/>
         <v>112.878</v>
       </c>
-      <c r="H127" s="11">
-        <v>0</v>
-      </c>
-      <c r="I127" s="5"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A128" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B128" s="11">
+      <c r="H129" s="11">
+        <v>0</v>
+      </c>
+      <c r="I129" s="5"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A130" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B130" s="11">
         <v>25</v>
       </c>
-      <c r="C128" s="11"/>
-      <c r="D128" s="11">
-        <v>0</v>
-      </c>
-      <c r="E128" s="11">
+      <c r="C130" s="11"/>
+      <c r="D130" s="11">
+        <v>0</v>
+      </c>
+      <c r="E130" s="11">
         <v>100</v>
       </c>
-      <c r="F128" s="11">
+      <c r="F130" s="11">
         <v>3.6300000000000003</v>
       </c>
-      <c r="G128" s="11">
+      <c r="G130" s="11">
         <f t="shared" si="3"/>
         <v>128.63</v>
       </c>
-      <c r="H128" s="11">
-        <v>0</v>
-      </c>
-      <c r="I128" s="5"/>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A129" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B129" s="11">
-        <v>0</v>
-      </c>
-      <c r="C129" s="11"/>
-      <c r="D129" s="11">
-        <v>0</v>
-      </c>
-      <c r="E129" s="11">
-        <v>0</v>
-      </c>
-      <c r="F129" s="11">
-        <v>0</v>
-      </c>
-      <c r="G129" s="11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H129" s="11">
-        <v>0</v>
-      </c>
-      <c r="I129" s="5"/>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A130" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B130" s="11">
-        <v>0</v>
-      </c>
-      <c r="C130" s="11"/>
-      <c r="D130" s="11">
-        <v>7130</v>
-      </c>
-      <c r="E130" s="11">
-        <v>0</v>
-      </c>
-      <c r="F130" s="11">
-        <v>328</v>
-      </c>
-      <c r="G130" s="11">
-        <f t="shared" si="3"/>
-        <v>7458</v>
-      </c>
       <c r="H130" s="11">
         <v>0</v>
       </c>
@@ -5351,24 +5363,24 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B131" s="11">
         <v>0</v>
       </c>
       <c r="C131" s="11"/>
       <c r="D131" s="11">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="E131" s="11">
         <v>0</v>
       </c>
       <c r="F131" s="11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G131" s="11">
-        <f t="shared" ref="G131:G145" si="4">SUM(B131:F131)</f>
-        <v>2400</v>
+        <f t="shared" ref="G131:G169" si="4">SUM(B131:F131)</f>
+        <v>0</v>
       </c>
       <c r="H131" s="11">
         <v>0</v>
@@ -5377,24 +5389,24 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B132" s="11">
         <v>0</v>
       </c>
       <c r="C132" s="11"/>
       <c r="D132" s="11">
-        <v>2148</v>
+        <v>7130</v>
       </c>
       <c r="E132" s="11">
         <v>0</v>
       </c>
       <c r="F132" s="11">
-        <v>55</v>
+        <v>328</v>
       </c>
       <c r="G132" s="11">
         <f t="shared" si="4"/>
-        <v>2203</v>
+        <v>7458</v>
       </c>
       <c r="H132" s="11">
         <v>0</v>
@@ -5403,24 +5415,24 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="10" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B133" s="11">
         <v>0</v>
       </c>
       <c r="C133" s="11"/>
       <c r="D133" s="11">
-        <v>4055</v>
+        <v>2300</v>
       </c>
       <c r="E133" s="11">
         <v>0</v>
       </c>
       <c r="F133" s="11">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="G133" s="11">
         <f t="shared" si="4"/>
-        <v>4185</v>
+        <v>2400</v>
       </c>
       <c r="H133" s="11">
         <v>0</v>
@@ -5429,24 +5441,24 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B134" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C134" s="11"/>
       <c r="D134" s="11">
-        <v>0</v>
+        <v>2148</v>
       </c>
       <c r="E134" s="11">
         <v>0</v>
       </c>
       <c r="F134" s="11">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G134" s="11">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>2203</v>
       </c>
       <c r="H134" s="11">
         <v>0</v>
@@ -5455,24 +5467,24 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="10" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B135" s="11">
         <v>0</v>
       </c>
       <c r="C135" s="11"/>
       <c r="D135" s="11">
-        <v>0</v>
+        <v>4055</v>
       </c>
       <c r="E135" s="11">
         <v>0</v>
       </c>
       <c r="F135" s="11">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="G135" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4185</v>
       </c>
       <c r="H135" s="11">
         <v>0</v>
@@ -5481,7 +5493,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B136" s="11">
         <v>0</v>
@@ -5507,7 +5519,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="10" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B137" s="11">
         <v>0</v>
@@ -5520,11 +5532,11 @@
         <v>0</v>
       </c>
       <c r="F137" s="11">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="G137" s="11">
         <f t="shared" si="4"/>
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H137" s="11">
         <v>0</v>
@@ -5533,7 +5545,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B138" s="11">
         <v>0</v>
@@ -5546,11 +5558,11 @@
         <v>0</v>
       </c>
       <c r="F138" s="11">
-        <v>258</v>
+        <v>442</v>
       </c>
       <c r="G138" s="11">
         <f t="shared" si="4"/>
-        <v>258</v>
+        <v>442</v>
       </c>
       <c r="H138" s="11">
         <v>0</v>
@@ -5559,10 +5571,10 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="10" t="s">
-        <v>246</v>
+        <v>50</v>
       </c>
       <c r="B139" s="11">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C139" s="11"/>
       <c r="D139" s="11">
@@ -5572,11 +5584,11 @@
         <v>0</v>
       </c>
       <c r="F139" s="11">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="G139" s="11">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="H139" s="11">
         <v>0</v>
@@ -5585,10 +5597,10 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="10" t="s">
-        <v>240</v>
+        <v>51</v>
       </c>
       <c r="B140" s="11">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C140" s="11"/>
       <c r="D140" s="11">
@@ -5602,7 +5614,7 @@
       </c>
       <c r="G140" s="11">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H140" s="11">
         <v>0</v>
@@ -5611,10 +5623,10 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="10" t="s">
-        <v>70</v>
+        <v>249</v>
       </c>
       <c r="B141" s="11">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C141" s="11"/>
       <c r="D141" s="11">
@@ -5628,7 +5640,7 @@
       </c>
       <c r="G141" s="11">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H141" s="11">
         <v>0</v>
@@ -5637,10 +5649,10 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="10" t="s">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="B142" s="11">
-        <v>1</v>
+        <v>82.5</v>
       </c>
       <c r="C142" s="11"/>
       <c r="D142" s="11">
@@ -5654,7 +5666,7 @@
       </c>
       <c r="G142" s="11">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>82.5</v>
       </c>
       <c r="H142" s="11">
         <v>0</v>
@@ -5663,10 +5675,10 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="10" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B143" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C143" s="11"/>
       <c r="D143" s="11">
@@ -5680,7 +5692,7 @@
       </c>
       <c r="G143" s="11">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="11">
         <v>0</v>
@@ -5689,10 +5701,10 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="10" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B144" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C144" s="11"/>
       <c r="D144" s="11">
@@ -5706,7 +5718,7 @@
       </c>
       <c r="G144" s="11">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H144" s="11">
         <v>0</v>
@@ -5715,10 +5727,10 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="10" t="s">
-        <v>241</v>
+        <v>55</v>
       </c>
       <c r="B145" s="11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C145" s="11"/>
       <c r="D145" s="11">
@@ -5732,7 +5744,7 @@
       </c>
       <c r="G145" s="11">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H145" s="11">
         <v>0</v>
@@ -5741,10 +5753,10 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B146" s="11">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="C146" s="11"/>
       <c r="D146" s="11">
@@ -5757,6 +5769,7 @@
         <v>0</v>
       </c>
       <c r="G146" s="11">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H146" s="11">
@@ -5766,7 +5779,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B147" s="11">
         <v>0</v>
@@ -5782,6 +5795,7 @@
         <v>0</v>
       </c>
       <c r="G147" s="11">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H147" s="11">
@@ -5791,7 +5805,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="10" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B148" s="11">
         <v>0</v>
@@ -5807,6 +5821,7 @@
         <v>0</v>
       </c>
       <c r="G148" s="11">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H148" s="11">
@@ -5816,10 +5831,10 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="10" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B149" s="11">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="C149" s="11"/>
       <c r="D149" s="11">
@@ -5832,6 +5847,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="11">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H149" s="11">
@@ -5841,7 +5857,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="10" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B150" s="11">
         <v>0</v>
@@ -5856,7 +5872,8 @@
       <c r="F150" s="13">
         <v>0</v>
       </c>
-      <c r="G150" s="13">
+      <c r="G150" s="11">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H150" s="13">
@@ -5865,23 +5882,24 @@
       <c r="I150" s="7"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A151" s="10" t="s">
-        <v>245</v>
+      <c r="A151" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="B151" s="11">
         <v>0</v>
       </c>
-      <c r="C151" s="13"/>
+      <c r="C151" s="11"/>
       <c r="D151" s="11">
         <v>0</v>
       </c>
       <c r="E151" s="11">
         <v>0</v>
       </c>
-      <c r="F151" s="13">
-        <v>0</v>
-      </c>
-      <c r="G151" s="13">
+      <c r="F151" s="11">
+        <v>0</v>
+      </c>
+      <c r="G151" s="11">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H151" s="13">
@@ -5890,29 +5908,404 @@
       <c r="I151" s="7"/>
     </row>
     <row r="152" spans="1:9" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="B152" s="14">
+      <c r="A152" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B152" s="11">
+        <v>0</v>
+      </c>
+      <c r="C152" s="11"/>
+      <c r="D152" s="11">
+        <v>0</v>
+      </c>
+      <c r="E152" s="11">
+        <v>0</v>
+      </c>
+      <c r="F152" s="11">
+        <v>0</v>
+      </c>
+      <c r="G152" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H152" s="14">
+        <v>0</v>
+      </c>
+      <c r="I152" s="8"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A153" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B153" s="11">
+        <v>0</v>
+      </c>
+      <c r="C153" s="11"/>
+      <c r="D153" s="11">
+        <v>0</v>
+      </c>
+      <c r="E153" s="11">
+        <v>0</v>
+      </c>
+      <c r="F153" s="11">
+        <v>0</v>
+      </c>
+      <c r="G153" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A154" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B154" s="11">
+        <v>0</v>
+      </c>
+      <c r="C154" s="11"/>
+      <c r="D154" s="11">
+        <v>0</v>
+      </c>
+      <c r="E154" s="11">
+        <v>0</v>
+      </c>
+      <c r="F154" s="11">
+        <v>0</v>
+      </c>
+      <c r="G154" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A155" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B155" s="11">
+        <v>0</v>
+      </c>
+      <c r="C155" s="11"/>
+      <c r="D155" s="11">
+        <v>0</v>
+      </c>
+      <c r="E155" s="11">
+        <v>0</v>
+      </c>
+      <c r="F155" s="11">
+        <v>0</v>
+      </c>
+      <c r="G155" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A156" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B156" s="11">
+        <v>0</v>
+      </c>
+      <c r="C156" s="11"/>
+      <c r="D156" s="11">
+        <v>0</v>
+      </c>
+      <c r="E156" s="11">
+        <v>0</v>
+      </c>
+      <c r="F156" s="11">
+        <v>0</v>
+      </c>
+      <c r="G156" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A157" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B157" s="11">
+        <v>0</v>
+      </c>
+      <c r="C157" s="11"/>
+      <c r="D157" s="11">
+        <v>0</v>
+      </c>
+      <c r="E157" s="11">
+        <v>0</v>
+      </c>
+      <c r="F157" s="11">
+        <v>0</v>
+      </c>
+      <c r="G157" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A158" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B158" s="11">
+        <v>9</v>
+      </c>
+      <c r="C158" s="11"/>
+      <c r="D158" s="11">
+        <v>0</v>
+      </c>
+      <c r="E158" s="11">
+        <v>0</v>
+      </c>
+      <c r="F158" s="11">
+        <v>0</v>
+      </c>
+      <c r="G158" s="11">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A159" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B159" s="11">
+        <v>1</v>
+      </c>
+      <c r="C159" s="11"/>
+      <c r="D159" s="11">
+        <v>0</v>
+      </c>
+      <c r="E159" s="11">
+        <v>0</v>
+      </c>
+      <c r="F159" s="11">
+        <v>0</v>
+      </c>
+      <c r="G159" s="11">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A160" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B160" s="11">
+        <v>1</v>
+      </c>
+      <c r="C160" s="11"/>
+      <c r="D160" s="11">
+        <v>0</v>
+      </c>
+      <c r="E160" s="11">
+        <v>0</v>
+      </c>
+      <c r="F160" s="11">
+        <v>0</v>
+      </c>
+      <c r="G160" s="11">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B161" s="11">
+        <v>16</v>
+      </c>
+      <c r="C161" s="11"/>
+      <c r="D161" s="11">
+        <v>0</v>
+      </c>
+      <c r="E161" s="11">
+        <v>0</v>
+      </c>
+      <c r="F161" s="11">
+        <v>0</v>
+      </c>
+      <c r="G161" s="11">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B162" s="11">
         <v>7</v>
       </c>
-      <c r="C152" s="15"/>
-      <c r="D152" s="14">
-        <v>0</v>
-      </c>
-      <c r="E152" s="14">
-        <v>0</v>
-      </c>
-      <c r="F152" s="15">
-        <v>0</v>
-      </c>
-      <c r="G152" s="15">
-        <v>0</v>
-      </c>
-      <c r="H152" s="15">
-        <v>0</v>
-      </c>
-      <c r="I152" s="8"/>
+      <c r="C162" s="11"/>
+      <c r="D162" s="11">
+        <v>0</v>
+      </c>
+      <c r="E162" s="11">
+        <v>0</v>
+      </c>
+      <c r="F162" s="11">
+        <v>0</v>
+      </c>
+      <c r="G162" s="11">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="B163" s="11">
+        <v>0</v>
+      </c>
+      <c r="C163" s="11"/>
+      <c r="D163" s="11">
+        <v>0</v>
+      </c>
+      <c r="E163" s="11">
+        <v>0</v>
+      </c>
+      <c r="F163" s="11">
+        <v>0</v>
+      </c>
+      <c r="G163" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B164" s="11">
+        <v>7</v>
+      </c>
+      <c r="C164" s="11"/>
+      <c r="D164" s="11">
+        <v>0</v>
+      </c>
+      <c r="E164" s="11">
+        <v>0</v>
+      </c>
+      <c r="F164" s="11">
+        <v>0</v>
+      </c>
+      <c r="G164" s="11">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A165" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B165" s="11">
+        <v>0</v>
+      </c>
+      <c r="C165" s="11"/>
+      <c r="D165" s="11">
+        <v>0</v>
+      </c>
+      <c r="E165" s="11">
+        <v>0</v>
+      </c>
+      <c r="F165" s="11">
+        <v>0</v>
+      </c>
+      <c r="G165" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A166" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B166" s="11">
+        <v>0</v>
+      </c>
+      <c r="C166" s="11"/>
+      <c r="D166" s="11">
+        <v>0</v>
+      </c>
+      <c r="E166" s="11">
+        <v>0</v>
+      </c>
+      <c r="F166" s="11">
+        <v>0</v>
+      </c>
+      <c r="G166" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A167" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B167" s="11">
+        <v>0</v>
+      </c>
+      <c r="C167" s="11"/>
+      <c r="D167" s="11">
+        <v>0</v>
+      </c>
+      <c r="E167" s="11">
+        <v>0</v>
+      </c>
+      <c r="F167" s="11">
+        <v>0</v>
+      </c>
+      <c r="G167" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A168" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B168" s="11">
+        <v>0</v>
+      </c>
+      <c r="C168" s="11"/>
+      <c r="D168" s="11">
+        <v>0</v>
+      </c>
+      <c r="E168" s="11">
+        <v>0</v>
+      </c>
+      <c r="F168" s="11">
+        <v>0</v>
+      </c>
+      <c r="G168" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A169" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B169" s="11">
+        <v>0</v>
+      </c>
+      <c r="C169" s="11"/>
+      <c r="D169" s="11">
+        <v>0</v>
+      </c>
+      <c r="E169" s="11">
+        <v>0</v>
+      </c>
+      <c r="F169" s="11">
+        <v>0</v>
+      </c>
+      <c r="G169" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection autoFilter="0"/>

--- a/جر د شهر 8.xlsx
+++ b/جر د شهر 8.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\جرد شهر 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D3EFD6-540F-48AA-9B1B-1F736B67DC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8A4A56-B48E-44F6-AA45-2AE34EC23FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14040" xr2:uid="{86282878-4084-4E7F-B814-2BEB8919EF4C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$H$375</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$H$374</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="252">
   <si>
     <t>اكياس برجر الهنا ص</t>
   </si>
@@ -111,9 +111,6 @@
     <t>اكياس كبده 3ك</t>
   </si>
   <si>
-    <t>كروت مفروم صويا ازرق 350</t>
-  </si>
-  <si>
     <t>كروت مفروم صافي 350</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t>اكياس s.p شفاف برجر</t>
   </si>
   <si>
-    <t>اكياس برجر ابوهاشم 1ك</t>
-  </si>
-  <si>
     <t>اكياس سجق s.p صغير</t>
   </si>
   <si>
@@ -255,9 +249,6 @@
     <t xml:space="preserve">استطوانة فريون </t>
   </si>
   <si>
-    <t xml:space="preserve">فلتر خاص بالثلاجة </t>
-  </si>
-  <si>
     <t xml:space="preserve">زيت سيارات </t>
   </si>
   <si>
@@ -759,9 +750,6 @@
     <t xml:space="preserve">شرش بودر </t>
   </si>
   <si>
-    <t>أكياس استربس ص SP</t>
-  </si>
-  <si>
     <t>أكياس بانيه الهنا 5 ك</t>
   </si>
   <si>
@@ -796,13 +784,22 @@
   </si>
   <si>
     <t>جرد شهر 8 لعام 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كروت برجر أبو هاشم </t>
+  </si>
+  <si>
+    <t xml:space="preserve">برجر أبو هاشم 1ك </t>
+  </si>
+  <si>
+    <t xml:space="preserve">كروت استربس </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -830,8 +827,141 @@
       <charset val="178"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="23"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="60"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="63"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color indexed="56"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -855,8 +985,113 @@
         <fgColor indexed="11"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="27"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="29"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="36"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="49"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="62"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1025,13 +1260,161 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="63"/>
+      </left>
+      <right style="double">
+        <color indexed="63"/>
+      </right>
+      <top style="double">
+        <color indexed="63"/>
+      </top>
+      <bottom style="double">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="62"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="30"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="52"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="62"/>
+      </top>
+      <bottom style="double">
+        <color indexed="62"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1058,11 +1441,54 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="44">
+    <cellStyle name="20% - Accent1" xfId="3" xr:uid="{98BF7EF2-0FB0-4F53-BF07-4F0204879330}"/>
+    <cellStyle name="20% - Accent2" xfId="4" xr:uid="{61FCF3CC-69D1-4D95-8826-05F1208358EF}"/>
+    <cellStyle name="20% - Accent3" xfId="5" xr:uid="{507B8746-5290-4963-9502-CAA611642737}"/>
+    <cellStyle name="20% - Accent4" xfId="6" xr:uid="{4B61ABEE-4455-4943-93AC-61552CC0C3E4}"/>
+    <cellStyle name="20% - Accent5" xfId="7" xr:uid="{E760FA76-6D12-44E0-9026-1A2A0A55ECFF}"/>
+    <cellStyle name="20% - Accent6" xfId="8" xr:uid="{835FBC51-BAC5-4D3F-9BF8-8B4FC146F677}"/>
+    <cellStyle name="40% - Accent1" xfId="9" xr:uid="{49F90F62-4207-4E6D-858E-B7B8920769A4}"/>
+    <cellStyle name="40% - Accent2" xfId="10" xr:uid="{6AE962DF-0A0D-4E32-834F-32D19360757F}"/>
+    <cellStyle name="40% - Accent3" xfId="11" xr:uid="{EB077589-326C-4917-B1E2-2896A8A2D79C}"/>
     <cellStyle name="40% - Accent3 2" xfId="2" xr:uid="{6FD4C5EA-656B-4A54-9048-8C03FFF91696}"/>
+    <cellStyle name="40% - Accent4" xfId="12" xr:uid="{8F1998A5-49AF-45A1-BF97-96EE3842AC83}"/>
+    <cellStyle name="40% - Accent5" xfId="13" xr:uid="{C2106FA8-F990-4671-A7A5-0F7673513D5A}"/>
+    <cellStyle name="40% - Accent6" xfId="14" xr:uid="{5EACC164-F7BB-42BA-A2BB-77E569060AD6}"/>
+    <cellStyle name="60% - Accent1" xfId="15" xr:uid="{A5FF2B1C-8CD5-4C68-8C72-77151C5C7046}"/>
+    <cellStyle name="60% - Accent2" xfId="16" xr:uid="{E934D724-9A35-4734-B5AB-15307F7F57B7}"/>
+    <cellStyle name="60% - Accent3" xfId="17" xr:uid="{B8744FB7-0A5F-483B-90F9-F16C6BF6576B}"/>
+    <cellStyle name="60% - Accent4" xfId="18" xr:uid="{D4ABCFFB-34CE-4AEA-9214-8DC1F1F82390}"/>
+    <cellStyle name="60% - Accent5" xfId="19" xr:uid="{B0B40576-1712-4E5D-ADC6-4D6517B519F5}"/>
+    <cellStyle name="60% - Accent6" xfId="20" xr:uid="{1F0E09F3-C85A-487F-B414-A7F2619BCE0A}"/>
+    <cellStyle name="Accent1" xfId="21" xr:uid="{51916046-9288-4605-83B1-F9439383DBFF}"/>
+    <cellStyle name="Accent2" xfId="22" xr:uid="{1BEFA8AC-68D2-4860-90C8-28604CE76EE1}"/>
+    <cellStyle name="Accent3" xfId="23" xr:uid="{FA6B71EF-CF1A-4515-938B-C05B91BB3E1B}"/>
+    <cellStyle name="Accent4" xfId="24" xr:uid="{F390CE8B-2702-4AD5-B30B-6604388BB80A}"/>
+    <cellStyle name="Accent5" xfId="25" xr:uid="{DDBA87CC-EB90-4908-A4CF-BD900FCD94AF}"/>
+    <cellStyle name="Accent6" xfId="26" xr:uid="{58AE080C-AB09-4396-B9F4-23891BEFF670}"/>
+    <cellStyle name="Bad" xfId="27" xr:uid="{C30D80BA-847D-4CBB-9960-64BE342AEE0B}"/>
+    <cellStyle name="Calculation" xfId="28" xr:uid="{92190C74-EA60-4384-A5B1-9C3AEA66B581}"/>
+    <cellStyle name="Check Cell" xfId="29" xr:uid="{ACD2E0A9-EEC8-46F1-A764-A832E8205C0C}"/>
+    <cellStyle name="Explanatory Text" xfId="30" xr:uid="{95AAD415-486B-4D03-8679-DD6EFD0E79AF}"/>
+    <cellStyle name="Good" xfId="31" xr:uid="{C6F96AA7-3CBF-4F5C-B87F-BAA6F9BD6F2E}"/>
+    <cellStyle name="Heading 1" xfId="32" xr:uid="{7DA58484-70E6-43CA-9FF6-582BA163965F}"/>
+    <cellStyle name="Heading 2" xfId="33" xr:uid="{3713F434-0C62-44F1-894E-3529126351B6}"/>
+    <cellStyle name="Heading 3" xfId="34" xr:uid="{41F8E502-442E-4D07-80A9-F4A03C9BDC83}"/>
+    <cellStyle name="Heading 4" xfId="35" xr:uid="{F3C33703-63F0-4CAB-9769-5D607BDD9ECA}"/>
+    <cellStyle name="Input" xfId="36" xr:uid="{7D6B1DE4-9F12-431F-B0AD-CA692504543A}"/>
+    <cellStyle name="Linked Cell" xfId="37" xr:uid="{899D87CD-D0C0-4671-A687-C4D69228AFBE}"/>
+    <cellStyle name="Neutral" xfId="38" xr:uid="{CF81082A-0AF5-4439-9D96-8EF23E785E9D}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CAB98B09-382F-4261-9B16-A82BDD194821}"/>
+    <cellStyle name="Note" xfId="39" xr:uid="{3157DEA9-BBDD-4235-9699-7909B97D4450}"/>
+    <cellStyle name="Output" xfId="40" xr:uid="{2E617861-6889-40D6-84DC-6738D9D08BFB}"/>
+    <cellStyle name="Title" xfId="41" xr:uid="{C437FD37-8E5D-41DF-A214-EADD331C7B5C}"/>
+    <cellStyle name="Total" xfId="42" xr:uid="{4D135EE2-9599-4AAC-B6BE-E010B175EC70}"/>
+    <cellStyle name="Warning Text" xfId="43" xr:uid="{D584DC6B-40E5-4D4E-8F13-B212D7A0A206}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1374,8 +1800,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69590074-F9E1-47CB-9D65-9D1D53B05140}">
-  <dimension ref="A2:I153"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:I152"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="35.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.140625" style="1" bestFit="1" customWidth="1"/>
@@ -1389,45 +1815,45 @@
     <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="D2" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="19.5" thickBot="1"/>
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="B5" s="11">
         <v>500</v>
@@ -1447,15 +1873,15 @@
         <v>500</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I5" s="5">
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B6" s="11">
         <v>1240.25</v>
@@ -1477,15 +1903,15 @@
         <v>1249.55</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I6" s="5">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B7" s="11">
         <v>320</v>
@@ -1505,15 +1931,15 @@
         <v>320</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I7" s="5">
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B8" s="11">
         <v>2110</v>
@@ -1535,15 +1961,15 @@
         <v>2120</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I8" s="5">
         <v>358</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B9" s="11">
         <v>1241</v>
@@ -1563,15 +1989,15 @@
         <v>1241</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I9" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B10" s="11">
         <v>680</v>
@@ -1593,15 +2019,15 @@
         <v>777</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I10" s="5">
         <v>201</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B11" s="11">
         <v>151.5</v>
@@ -1621,15 +2047,15 @@
         <v>151.5</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I11" s="5">
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B12" s="11">
         <v>415</v>
@@ -1649,15 +2075,15 @@
         <v>415</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I12" s="5">
         <v>278</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B13" s="11">
         <v>1751.1999999999998</v>
@@ -1679,15 +2105,15 @@
         <v>1754.85</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I13" s="5">
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B14" s="11">
         <v>20</v>
@@ -1709,15 +2135,15 @@
         <v>40</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I14" s="5">
         <v>147</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B15" s="11">
         <v>40</v>
@@ -1739,15 +2165,15 @@
         <v>60</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I15" s="5">
         <v>240</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B16" s="11">
         <v>0</v>
@@ -1769,15 +2195,15 @@
         <v>20</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B17" s="11">
         <v>5</v>
@@ -1799,15 +2225,15 @@
         <v>25</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I17" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B18" s="11">
         <v>0</v>
@@ -1827,15 +2253,15 @@
         <v>0</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I18" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B19" s="11">
         <v>106</v>
@@ -1857,15 +2283,15 @@
         <v>110</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I19" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B20" s="11">
         <v>3090</v>
@@ -1887,15 +2313,15 @@
         <v>3325</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="A21" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B21" s="11">
         <v>180</v>
@@ -1915,15 +2341,15 @@
         <v>180</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I21" s="5">
         <v>4200</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="A22" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B22" s="11">
         <v>63.30400000000003</v>
@@ -1943,15 +2369,15 @@
         <v>63.30400000000003</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B23" s="11">
         <v>359</v>
@@ -1971,15 +2397,15 @@
         <v>359</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24" s="10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B24" s="11">
         <v>118</v>
@@ -1999,15 +2425,15 @@
         <v>118</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I24" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="A25" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B25" s="11">
         <v>470</v>
@@ -2027,15 +2453,15 @@
         <v>470</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B26" s="11">
         <v>15.7</v>
@@ -2055,15 +2481,15 @@
         <v>15.7</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27" s="10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B27" s="11">
         <v>0</v>
@@ -2083,15 +2509,15 @@
         <v>0</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I27" s="5">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B28" s="11">
         <v>0</v>
@@ -2111,15 +2537,15 @@
         <v>0</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B29" s="11">
         <v>0</v>
@@ -2139,15 +2565,15 @@
         <v>0</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30" s="10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B30" s="11">
         <v>0</v>
@@ -2167,15 +2593,15 @@
         <v>0</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I30" s="5">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="A31" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B31" s="11">
         <v>0</v>
@@ -2195,15 +2621,15 @@
         <v>0</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I31" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="A32" s="10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B32" s="11">
         <v>0</v>
@@ -2223,15 +2649,15 @@
         <v>0</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I32" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9">
       <c r="A33" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B33" s="11">
         <v>0</v>
@@ -2251,15 +2677,15 @@
         <v>0</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I33" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9">
       <c r="A34" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B34" s="11">
         <v>0</v>
@@ -2279,15 +2705,15 @@
         <v>0</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I34" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9">
       <c r="A35" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B35" s="11">
         <v>0</v>
@@ -2307,15 +2733,15 @@
         <v>0</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I35" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9">
       <c r="A36" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B36" s="11">
         <v>400</v>
@@ -2335,15 +2761,15 @@
         <v>400</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I36" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9">
       <c r="A37" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B37" s="11">
         <v>36.379999999999995</v>
@@ -2363,15 +2789,15 @@
         <v>36.379999999999995</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I37" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9">
       <c r="A38" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B38" s="11">
         <v>5.0999999999999996</v>
@@ -2391,15 +2817,15 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I38" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9">
       <c r="A39" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B39" s="11">
         <v>14.9</v>
@@ -2419,15 +2845,15 @@
         <v>14.9</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I39" s="5">
         <v>247</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9">
       <c r="A40" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B40" s="11">
         <v>0</v>
@@ -2447,15 +2873,15 @@
         <v>0</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I40" s="5">
         <v>1009</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9">
       <c r="A41" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B41" s="11">
         <v>10.6</v>
@@ -2475,15 +2901,15 @@
         <v>10.6</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I41" s="5">
         <v>1043</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9">
       <c r="A42" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B42" s="11">
         <v>10</v>
@@ -2503,15 +2929,15 @@
         <v>10</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I42" s="5">
         <v>1885</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9">
       <c r="A43" s="10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B43" s="11">
         <v>12.5</v>
@@ -2531,15 +2957,15 @@
         <v>12.5</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I43" s="5">
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9">
       <c r="A44" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B44" s="11">
         <v>4.9749999999999996</v>
@@ -2559,15 +2985,15 @@
         <v>4.9749999999999996</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I44" s="5">
         <v>680</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9">
       <c r="A45" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B45" s="11">
         <v>55</v>
@@ -2587,15 +3013,15 @@
         <v>55</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I45" s="5">
         <v>1051</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9">
       <c r="A46" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B46" s="11">
         <v>23.7</v>
@@ -2615,15 +3041,15 @@
         <v>23.7</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I46" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9">
       <c r="A47" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B47" s="11">
         <v>3</v>
@@ -2643,15 +3069,15 @@
         <v>3</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I47" s="5">
         <v>121</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9">
       <c r="A48" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B48" s="11">
         <v>63</v>
@@ -2671,15 +3097,15 @@
         <v>63</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I48" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9">
       <c r="A49" s="10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B49" s="11">
         <v>1.7899999999999998</v>
@@ -2699,15 +3125,15 @@
         <v>1.7899999999999998</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I49" s="5">
         <v>483</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9">
       <c r="A50" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B50" s="11">
         <v>10.44</v>
@@ -2727,15 +3153,15 @@
         <v>10.44</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I50" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9">
       <c r="A51" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B51" s="11">
         <v>9.1999999999999993</v>
@@ -2755,15 +3181,15 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I51" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9">
       <c r="A52" s="10" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B52" s="11">
         <v>0</v>
@@ -2783,15 +3209,15 @@
         <v>0</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I52" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9">
       <c r="A53" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B53" s="11">
         <v>31.700000000000003</v>
@@ -2811,15 +3237,15 @@
         <v>31.700000000000003</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I53" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9">
       <c r="A54" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B54" s="11">
         <v>9.5</v>
@@ -2839,15 +3265,15 @@
         <v>9.5</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I54" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9">
       <c r="A55" s="10" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B55" s="11">
         <v>742</v>
@@ -2867,15 +3293,15 @@
         <v>742</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I55" s="5">
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9">
       <c r="A56" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B56" s="11">
         <v>212</v>
@@ -2895,15 +3321,15 @@
         <v>212</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I56" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9">
       <c r="A57" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B57" s="11">
         <v>127.5</v>
@@ -2923,15 +3349,15 @@
         <v>127.5</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I57" s="5">
         <v>868</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9">
       <c r="A58" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B58" s="11">
         <v>5.25</v>
@@ -2951,15 +3377,15 @@
         <v>5.25</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>626</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9">
       <c r="A59" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B59" s="11">
         <v>0</v>
@@ -2979,15 +3405,15 @@
         <v>0</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I59" s="5">
         <v>876</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9">
       <c r="A60" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B60" s="11">
         <v>19.305</v>
@@ -3007,15 +3433,15 @@
         <v>19.305</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I60" s="6">
         <v>1155</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9">
       <c r="A61" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B61" s="11">
         <v>31.5</v>
@@ -3035,15 +3461,15 @@
         <v>31.5</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I61" s="5">
         <v>68</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9">
       <c r="A62" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B62" s="11">
         <v>7.2</v>
@@ -3063,15 +3489,15 @@
         <v>7.2</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I62" s="5">
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9">
       <c r="A63" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B63" s="11">
         <v>9.5</v>
@@ -3091,15 +3517,15 @@
         <v>9.5</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I63" s="5">
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9">
       <c r="A64" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B64" s="11">
         <v>17.5</v>
@@ -3119,15 +3545,15 @@
         <v>17.5</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I64" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9">
       <c r="A65" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B65" s="11">
         <v>0</v>
@@ -3147,15 +3573,15 @@
         <v>0</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I65" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9">
       <c r="A66" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B66" s="11">
         <v>1.35</v>
@@ -3175,15 +3601,15 @@
         <v>1.35</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9">
       <c r="A67" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B67" s="11">
         <v>21.95</v>
@@ -3203,15 +3629,15 @@
         <v>21.95</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I67" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9">
       <c r="A68" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B68" s="11">
         <v>3.4949999999999997</v>
@@ -3231,15 +3657,15 @@
         <v>3.4949999999999997</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9">
       <c r="A69" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B69" s="11">
         <v>0</v>
@@ -3259,15 +3685,15 @@
         <v>0</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I69" s="5">
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9">
       <c r="A70" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B70" s="11">
         <v>10.664999999999999</v>
@@ -3287,15 +3713,15 @@
         <v>10.664999999999999</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I70" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9">
       <c r="A71" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B71" s="11">
         <v>0</v>
@@ -3315,15 +3741,15 @@
         <v>0</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I71" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9">
       <c r="A72" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B72" s="11">
         <v>6</v>
@@ -3343,15 +3769,15 @@
         <v>6</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I72" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9">
       <c r="A73" s="10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B73" s="11">
         <v>0</v>
@@ -3371,15 +3797,15 @@
         <v>0</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I73" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9">
       <c r="A74" s="10" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B74" s="11">
         <v>4.33</v>
@@ -3399,15 +3825,15 @@
         <v>4.33</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I74" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9">
       <c r="A75" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B75" s="11">
         <v>34.6</v>
@@ -3427,15 +3853,15 @@
         <v>34.6</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I75" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9">
       <c r="A76" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B76" s="11">
         <v>2.3999999999999995</v>
@@ -3455,15 +3881,15 @@
         <v>2.3999999999999995</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I76" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9">
       <c r="A77" s="10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B77" s="11">
         <v>18</v>
@@ -3483,15 +3909,15 @@
         <v>18</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I77" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9">
       <c r="A78" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B78" s="11">
         <v>0</v>
@@ -3511,15 +3937,15 @@
         <v>14451</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I78" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9">
       <c r="A79" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B79" s="11">
         <v>700</v>
@@ -3539,15 +3965,15 @@
         <v>731</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I79" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9">
       <c r="A80" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B80" s="11">
         <v>28</v>
@@ -3567,22 +3993,22 @@
         <v>67</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I80" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9">
       <c r="A81" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B81" s="11">
         <v>0</v>
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11">
-        <v>1384</v>
+        <v>754</v>
       </c>
       <c r="E81" s="11">
         <v>0</v>
@@ -3592,18 +4018,18 @@
       </c>
       <c r="G81" s="11">
         <f t="shared" si="2"/>
-        <v>1384</v>
+        <v>754</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I81" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9">
       <c r="A82" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B82" s="11">
         <v>484</v>
@@ -3623,15 +4049,15 @@
         <v>489</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I82" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9">
       <c r="A83" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B83" s="11">
         <v>1</v>
@@ -3651,13 +4077,13 @@
         <v>1</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I83" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9">
       <c r="A84" s="10" t="s">
         <v>0</v>
       </c>
@@ -3669,23 +4095,23 @@
         <v>0</v>
       </c>
       <c r="E84" s="11">
-        <v>420</v>
+        <v>642.5</v>
       </c>
       <c r="F84" s="11">
         <v>46</v>
       </c>
-      <c r="G84" s="11">
+      <c r="G84" s="16">
         <f t="shared" si="2"/>
-        <v>486</v>
+        <v>708.5</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I84" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9">
       <c r="A85" s="10" t="s">
         <v>1</v>
       </c>
@@ -3697,23 +4123,23 @@
         <v>0</v>
       </c>
       <c r="E85" s="11">
-        <v>90</v>
+        <v>499.29999999999995</v>
       </c>
       <c r="F85" s="11">
         <v>9.5</v>
       </c>
-      <c r="G85" s="11">
+      <c r="G85" s="16">
         <f t="shared" si="2"/>
-        <v>159.5</v>
+        <v>568.79999999999995</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I85" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9">
       <c r="A86" s="10" t="s">
         <v>2</v>
       </c>
@@ -3725,23 +4151,23 @@
         <v>0</v>
       </c>
       <c r="E86" s="11">
-        <v>120</v>
+        <v>302.5</v>
       </c>
       <c r="F86" s="11">
         <v>37</v>
       </c>
-      <c r="G86" s="11">
+      <c r="G86" s="16">
         <f t="shared" si="2"/>
-        <v>177</v>
+        <v>359.5</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I86" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9">
       <c r="A87" s="10" t="s">
         <v>3</v>
       </c>
@@ -3753,23 +4179,23 @@
         <v>0</v>
       </c>
       <c r="E87" s="11">
-        <v>480</v>
+        <v>380</v>
       </c>
       <c r="F87" s="11">
         <v>30</v>
       </c>
-      <c r="G87" s="11">
+      <c r="G87" s="16">
         <f t="shared" si="2"/>
-        <v>570</v>
+        <v>470</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I87" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9">
       <c r="A88" s="10" t="s">
         <v>4</v>
       </c>
@@ -3786,18 +4212,18 @@
       <c r="F88" s="11">
         <v>0</v>
       </c>
-      <c r="G88" s="11">
+      <c r="G88" s="16">
         <f t="shared" si="2"/>
         <v>45.6</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I88" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9">
       <c r="A89" s="10" t="s">
         <v>5</v>
       </c>
@@ -3809,23 +4235,23 @@
         <v>89</v>
       </c>
       <c r="E89" s="11">
-        <v>411.7</v>
+        <v>381.7</v>
       </c>
       <c r="F89" s="11">
         <v>24</v>
       </c>
-      <c r="G89" s="11">
+      <c r="G89" s="16">
         <f t="shared" si="2"/>
-        <v>524.70000000000005</v>
+        <v>494.7</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I89" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9">
       <c r="A90" s="10" t="s">
         <v>6</v>
       </c>
@@ -3837,23 +4263,23 @@
         <v>0</v>
       </c>
       <c r="E90" s="11">
-        <v>30</v>
+        <v>262.5</v>
       </c>
       <c r="F90" s="11">
         <v>10.5</v>
       </c>
-      <c r="G90" s="11">
+      <c r="G90" s="16">
         <f t="shared" si="2"/>
-        <v>60.5</v>
+        <v>293</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I90" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9">
       <c r="A91" s="10" t="s">
         <v>7</v>
       </c>
@@ -3870,18 +4296,18 @@
       <c r="F91" s="11">
         <v>13</v>
       </c>
-      <c r="G91" s="11">
+      <c r="G91" s="16">
         <f t="shared" si="2"/>
         <v>373</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I91" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9">
       <c r="A92" s="10" t="s">
         <v>8</v>
       </c>
@@ -3898,18 +4324,18 @@
       <c r="F92" s="11">
         <v>7</v>
       </c>
-      <c r="G92" s="11">
+      <c r="G92" s="16">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I92" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9">
       <c r="A93" s="10" t="s">
         <v>9</v>
       </c>
@@ -3926,18 +4352,18 @@
       <c r="F93" s="11">
         <v>0</v>
       </c>
-      <c r="G93" s="11">
+      <c r="G93" s="16">
         <f t="shared" si="2"/>
         <v>4.8499999999999996</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I93" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9">
       <c r="A94" s="10" t="s">
         <v>10</v>
       </c>
@@ -3954,18 +4380,18 @@
       <c r="F94" s="11">
         <v>23</v>
       </c>
-      <c r="G94" s="11">
+      <c r="G94" s="16">
         <f t="shared" si="2"/>
         <v>88.8</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I94" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9">
       <c r="A95" s="10" t="s">
         <v>11</v>
       </c>
@@ -3982,18 +4408,18 @@
       <c r="F95" s="11">
         <v>0</v>
       </c>
-      <c r="G95" s="11">
+      <c r="G95" s="16">
         <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I95" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9">
       <c r="A96" s="10" t="s">
         <v>12</v>
       </c>
@@ -4010,18 +4436,18 @@
       <c r="F96" s="11">
         <v>0</v>
       </c>
-      <c r="G96" s="11">
+      <c r="G96" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I96" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9">
       <c r="A97" s="10" t="s">
         <v>13</v>
       </c>
@@ -4033,23 +4459,23 @@
         <v>0</v>
       </c>
       <c r="E97" s="11">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F97" s="11">
         <v>27</v>
       </c>
-      <c r="G97" s="11">
+      <c r="G97" s="16">
         <f t="shared" si="2"/>
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I97" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9">
       <c r="A98" s="10" t="s">
         <v>14</v>
       </c>
@@ -4066,18 +4492,18 @@
       <c r="F98" s="11">
         <v>14.633000000000001</v>
       </c>
-      <c r="G98" s="11">
+      <c r="G98" s="16">
         <f t="shared" si="2"/>
         <v>35.933</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I98" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9">
       <c r="A99" s="10" t="s">
         <v>15</v>
       </c>
@@ -4094,18 +4520,18 @@
       <c r="F99" s="11">
         <v>5.29</v>
       </c>
-      <c r="G99" s="11">
+      <c r="G99" s="16">
         <f t="shared" si="2"/>
         <v>5.29</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I99" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9">
       <c r="A100" s="10" t="s">
         <v>16</v>
       </c>
@@ -4122,18 +4548,18 @@
       <c r="F100" s="11">
         <v>140.47400000000005</v>
       </c>
-      <c r="G100" s="11">
+      <c r="G100" s="16">
         <f t="shared" si="2"/>
         <v>140.47400000000005</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I100" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9">
       <c r="A101" s="10" t="s">
         <v>17</v>
       </c>
@@ -4150,18 +4576,18 @@
       <c r="F101" s="11">
         <v>200</v>
       </c>
-      <c r="G101" s="11">
-        <f t="shared" ref="G101:G131" si="3">SUM(B101:F101)</f>
+      <c r="G101" s="16">
+        <f t="shared" ref="G101:G130" si="3">SUM(B101:F101)</f>
         <v>44700</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I101" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9">
       <c r="A102" s="10" t="s">
         <v>18</v>
       </c>
@@ -4178,18 +4604,18 @@
       <c r="F102" s="11">
         <v>1200</v>
       </c>
-      <c r="G102" s="11">
+      <c r="G102" s="16">
         <f t="shared" si="3"/>
         <v>21200</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I102" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9">
       <c r="A103" s="10" t="s">
         <v>19</v>
       </c>
@@ -4206,18 +4632,18 @@
       <c r="F103" s="11">
         <v>0</v>
       </c>
-      <c r="G103" s="11">
+      <c r="G103" s="16">
         <f t="shared" si="3"/>
         <v>260</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I103" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9">
       <c r="A104" s="10" t="s">
         <v>20</v>
       </c>
@@ -4234,18 +4660,18 @@
       <c r="F104" s="11">
         <v>18.600000000000001</v>
       </c>
-      <c r="G104" s="11">
+      <c r="G104" s="16">
         <f t="shared" si="3"/>
         <v>68.599999999999994</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I104" s="5">
         <v>1091</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9">
       <c r="A105" s="10" t="s">
         <v>21</v>
       </c>
@@ -4262,18 +4688,18 @@
       <c r="F105" s="11">
         <v>0</v>
       </c>
-      <c r="G105" s="11">
+      <c r="G105" s="16">
         <f t="shared" si="3"/>
         <v>51.900000000000006</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I105" s="5">
         <v>1090</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9">
       <c r="A106" s="10" t="s">
         <v>22</v>
       </c>
@@ -4290,7 +4716,7 @@
       <c r="F106" s="11">
         <v>0</v>
       </c>
-      <c r="G106" s="11">
+      <c r="G106" s="16">
         <f t="shared" si="3"/>
         <v>48.650000000000006</v>
       </c>
@@ -4299,7 +4725,7 @@
       </c>
       <c r="I106" s="5"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9">
       <c r="A107" s="10" t="s">
         <v>23</v>
       </c>
@@ -4316,7 +4742,7 @@
       <c r="F107" s="11">
         <v>10.4</v>
       </c>
-      <c r="G107" s="11">
+      <c r="G107" s="16">
         <f t="shared" si="3"/>
         <v>21.3</v>
       </c>
@@ -4325,9 +4751,9 @@
       </c>
       <c r="I107" s="5"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9">
       <c r="A108" s="10" t="s">
-        <v>24</v>
+        <v>251</v>
       </c>
       <c r="B108" s="11">
         <v>0</v>
@@ -4342,7 +4768,7 @@
       <c r="F108" s="11">
         <v>2000</v>
       </c>
-      <c r="G108" s="11">
+      <c r="G108" s="16">
         <f t="shared" si="3"/>
         <v>2000</v>
       </c>
@@ -4351,9 +4777,9 @@
       </c>
       <c r="I108" s="5"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9">
       <c r="A109" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B109" s="11">
         <v>0</v>
@@ -4368,7 +4794,7 @@
       <c r="F109" s="11">
         <v>9225</v>
       </c>
-      <c r="G109" s="11">
+      <c r="G109" s="16">
         <f t="shared" si="3"/>
         <v>9225</v>
       </c>
@@ -4377,9 +4803,9 @@
       </c>
       <c r="I109" s="5"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9">
       <c r="A110" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B110" s="11">
         <v>0</v>
@@ -4394,7 +4820,7 @@
       <c r="F110" s="11">
         <v>8786</v>
       </c>
-      <c r="G110" s="11">
+      <c r="G110" s="16">
         <f t="shared" si="3"/>
         <v>8786</v>
       </c>
@@ -4403,9 +4829,9 @@
       </c>
       <c r="I110" s="5"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9">
       <c r="A111" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B111" s="11">
         <v>81.5</v>
@@ -4415,23 +4841,23 @@
         <v>0</v>
       </c>
       <c r="E111" s="11">
-        <v>566</v>
+        <v>476</v>
       </c>
       <c r="F111" s="11">
         <v>26</v>
       </c>
-      <c r="G111" s="11">
+      <c r="G111" s="16">
         <f t="shared" si="3"/>
-        <v>673.5</v>
+        <v>583.5</v>
       </c>
       <c r="H111" s="11">
         <v>0</v>
       </c>
       <c r="I111" s="5"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9">
       <c r="A112" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B112" s="11">
         <v>0</v>
@@ -4446,7 +4872,7 @@
       <c r="F112" s="11">
         <v>13.8</v>
       </c>
-      <c r="G112" s="11">
+      <c r="G112" s="16">
         <f t="shared" si="3"/>
         <v>13.8</v>
       </c>
@@ -4455,16 +4881,16 @@
       </c>
       <c r="I112" s="5"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9">
       <c r="A113" s="10" t="s">
-        <v>29</v>
+        <v>249</v>
       </c>
       <c r="B113" s="11">
         <v>0</v>
       </c>
       <c r="C113" s="11"/>
       <c r="D113" s="11">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E113" s="11">
         <v>0</v>
@@ -4472,18 +4898,18 @@
       <c r="F113" s="11">
         <v>2000</v>
       </c>
-      <c r="G113" s="11">
+      <c r="G113" s="16">
         <f t="shared" si="3"/>
-        <v>2036</v>
+        <v>2000</v>
       </c>
       <c r="H113" s="11">
         <v>0</v>
       </c>
       <c r="I113" s="5"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9">
       <c r="A114" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B114" s="11">
         <v>0</v>
@@ -4496,20 +4922,20 @@
         <v>140</v>
       </c>
       <c r="F114" s="11">
-        <v>6.1280000000000001</v>
-      </c>
-      <c r="G114" s="11">
+        <v>48.3</v>
+      </c>
+      <c r="G114" s="16">
         <f t="shared" si="3"/>
-        <v>146.12799999999999</v>
+        <v>188.3</v>
       </c>
       <c r="H114" s="11">
         <v>0</v>
       </c>
       <c r="I114" s="5"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9">
       <c r="A115" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B115" s="11">
         <v>0</v>
@@ -4522,20 +4948,20 @@
         <v>240</v>
       </c>
       <c r="F115" s="11">
-        <v>48.3</v>
-      </c>
-      <c r="G115" s="11">
+        <v>120</v>
+      </c>
+      <c r="G115" s="16">
         <f t="shared" si="3"/>
-        <v>288.3</v>
+        <v>360</v>
       </c>
       <c r="H115" s="11">
         <v>0</v>
       </c>
       <c r="I115" s="5"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9">
       <c r="A116" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B116" s="11">
         <v>8.3000000000000007</v>
@@ -4545,23 +4971,23 @@
         <v>0</v>
       </c>
       <c r="E116" s="11">
-        <v>231.65</v>
+        <v>198.25</v>
       </c>
       <c r="F116" s="11">
-        <v>120</v>
-      </c>
-      <c r="G116" s="11">
+        <v>53</v>
+      </c>
+      <c r="G116" s="16">
         <f t="shared" si="3"/>
-        <v>359.95000000000005</v>
+        <v>259.55</v>
       </c>
       <c r="H116" s="11">
         <v>0</v>
       </c>
       <c r="I116" s="5"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9">
       <c r="A117" s="10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B117" s="11">
         <v>16.600000000000001</v>
@@ -4571,23 +4997,23 @@
         <v>0</v>
       </c>
       <c r="E117" s="11">
-        <v>463.35</v>
+        <v>421.75</v>
       </c>
       <c r="F117" s="11">
-        <v>53</v>
-      </c>
-      <c r="G117" s="11">
+        <v>18</v>
+      </c>
+      <c r="G117" s="16">
         <f t="shared" si="3"/>
-        <v>532.95000000000005</v>
+        <v>456.35</v>
       </c>
       <c r="H117" s="11">
         <v>0</v>
       </c>
       <c r="I117" s="5"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9">
       <c r="A118" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B118" s="11">
         <v>30</v>
@@ -4597,23 +5023,23 @@
         <v>0</v>
       </c>
       <c r="E118" s="11">
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="F118" s="11">
-        <v>18</v>
-      </c>
-      <c r="G118" s="11">
+        <v>19</v>
+      </c>
+      <c r="G118" s="16">
         <f t="shared" si="3"/>
-        <v>768</v>
+        <v>709</v>
       </c>
       <c r="H118" s="11">
         <v>0</v>
       </c>
       <c r="I118" s="5"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9">
       <c r="A119" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B119" s="11">
         <v>30</v>
@@ -4623,23 +5049,23 @@
         <v>0</v>
       </c>
       <c r="E119" s="11">
-        <v>774.3</v>
+        <v>743.5</v>
       </c>
       <c r="F119" s="11">
-        <v>19</v>
-      </c>
-      <c r="G119" s="11">
+        <v>21.8</v>
+      </c>
+      <c r="G119" s="16">
         <f t="shared" si="3"/>
-        <v>823.3</v>
+        <v>795.3</v>
       </c>
       <c r="H119" s="11">
         <v>0</v>
       </c>
       <c r="I119" s="5"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9">
       <c r="A120" s="10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B120" s="11">
         <v>73</v>
@@ -4649,23 +5075,23 @@
         <v>0</v>
       </c>
       <c r="E120" s="11">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="F120" s="11">
-        <v>21.8</v>
-      </c>
-      <c r="G120" s="11">
+        <v>14</v>
+      </c>
+      <c r="G120" s="16">
         <f t="shared" si="3"/>
-        <v>274.8</v>
+        <v>177</v>
       </c>
       <c r="H120" s="11">
         <v>0</v>
       </c>
       <c r="I120" s="5"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9">
       <c r="A121" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B121" s="11">
         <v>0</v>
@@ -4678,20 +5104,20 @@
         <v>0</v>
       </c>
       <c r="F121" s="11">
-        <v>14</v>
-      </c>
-      <c r="G121" s="11">
+        <v>827</v>
+      </c>
+      <c r="G121" s="16">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>827</v>
       </c>
       <c r="H121" s="11">
         <v>0</v>
       </c>
       <c r="I121" s="5"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9">
       <c r="A122" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B122" s="11">
         <v>0</v>
@@ -4704,20 +5130,20 @@
         <v>0</v>
       </c>
       <c r="F122" s="11">
-        <v>827</v>
-      </c>
-      <c r="G122" s="11">
+        <v>0</v>
+      </c>
+      <c r="G122" s="16">
         <f t="shared" si="3"/>
-        <v>827</v>
+        <v>0</v>
       </c>
       <c r="H122" s="11">
         <v>0</v>
       </c>
       <c r="I122" s="5"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9">
       <c r="A123" s="10" t="s">
-        <v>240</v>
+        <v>37</v>
       </c>
       <c r="B123" s="11">
         <v>0</v>
@@ -4730,20 +5156,20 @@
         <v>0</v>
       </c>
       <c r="F123" s="11">
-        <v>379</v>
-      </c>
-      <c r="G123" s="11">
+        <v>0</v>
+      </c>
+      <c r="G123" s="16">
         <f t="shared" si="3"/>
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="H123" s="11">
         <v>0</v>
       </c>
       <c r="I123" s="5"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9">
       <c r="A124" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B124" s="11">
         <v>0</v>
@@ -4756,20 +5182,20 @@
         <v>0</v>
       </c>
       <c r="F124" s="11">
-        <v>0</v>
-      </c>
-      <c r="G124" s="11">
+        <v>1073</v>
+      </c>
+      <c r="G124" s="16">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1073</v>
       </c>
       <c r="H124" s="11">
         <v>0</v>
       </c>
       <c r="I124" s="5"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9">
       <c r="A125" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B125" s="11">
         <v>0</v>
@@ -4782,23 +5208,23 @@
         <v>0</v>
       </c>
       <c r="F125" s="11">
-        <v>1073</v>
-      </c>
-      <c r="G125" s="11">
+        <v>0</v>
+      </c>
+      <c r="G125" s="16">
         <f t="shared" si="3"/>
-        <v>1073</v>
+        <v>0</v>
       </c>
       <c r="H125" s="11">
         <v>0</v>
       </c>
       <c r="I125" s="5"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9">
       <c r="A126" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B126" s="11">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="C126" s="11"/>
       <c r="D126" s="11">
@@ -4810,47 +5236,47 @@
       <c r="F126" s="11">
         <v>0</v>
       </c>
-      <c r="G126" s="11">
+      <c r="G126" s="16">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="H126" s="11">
         <v>0</v>
       </c>
       <c r="I126" s="5"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9">
       <c r="A127" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B127" s="11">
-        <v>11.8</v>
+        <v>11.25</v>
       </c>
       <c r="C127" s="11"/>
       <c r="D127" s="11">
         <v>0</v>
       </c>
       <c r="E127" s="11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F127" s="11">
-        <v>0</v>
-      </c>
-      <c r="G127" s="11">
+        <v>1.6279999999999999</v>
+      </c>
+      <c r="G127" s="16">
         <f t="shared" si="3"/>
-        <v>11.8</v>
+        <v>112.878</v>
       </c>
       <c r="H127" s="11">
         <v>0</v>
       </c>
       <c r="I127" s="5"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9">
       <c r="A128" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B128" s="11">
-        <v>11.25</v>
+        <v>25</v>
       </c>
       <c r="C128" s="11"/>
       <c r="D128" s="11">
@@ -4859,180 +5285,180 @@
       <c r="E128" s="11">
         <v>100</v>
       </c>
-      <c r="F128" s="11">
-        <v>1.6279999999999999</v>
-      </c>
-      <c r="G128" s="11">
+      <c r="F128" s="17">
+        <v>3.6300000000000003</v>
+      </c>
+      <c r="G128" s="16">
         <f t="shared" si="3"/>
-        <v>112.878</v>
+        <v>128.63</v>
       </c>
       <c r="H128" s="11">
         <v>0</v>
       </c>
       <c r="I128" s="5"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9">
       <c r="A129" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B129" s="11">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C129" s="11"/>
       <c r="D129" s="11">
         <v>0</v>
       </c>
       <c r="E129" s="11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F129" s="11">
-        <v>3.6300000000000003</v>
+        <v>0</v>
       </c>
       <c r="G129" s="11">
         <f t="shared" si="3"/>
-        <v>128.63</v>
+        <v>0</v>
       </c>
       <c r="H129" s="11">
         <v>0</v>
       </c>
       <c r="I129" s="5"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9">
       <c r="A130" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B130" s="11">
         <v>0</v>
       </c>
       <c r="C130" s="11"/>
       <c r="D130" s="11">
-        <v>0</v>
+        <v>7130</v>
       </c>
       <c r="E130" s="11">
         <v>0</v>
       </c>
       <c r="F130" s="11">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="G130" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7458</v>
       </c>
       <c r="H130" s="11">
         <v>0</v>
       </c>
       <c r="I130" s="5"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9">
       <c r="A131" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B131" s="11">
         <v>0</v>
       </c>
       <c r="C131" s="11"/>
       <c r="D131" s="11">
-        <v>2955</v>
+        <v>2300</v>
       </c>
       <c r="E131" s="11">
         <v>0</v>
       </c>
       <c r="F131" s="11">
-        <v>328</v>
+        <v>100</v>
       </c>
       <c r="G131" s="11">
-        <f t="shared" si="3"/>
-        <v>3283</v>
+        <f t="shared" ref="G131:G145" si="4">SUM(B131:F131)</f>
+        <v>2400</v>
       </c>
       <c r="H131" s="11">
         <v>0</v>
       </c>
       <c r="I131" s="5"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9">
       <c r="A132" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B132" s="11">
         <v>0</v>
       </c>
       <c r="C132" s="11"/>
       <c r="D132" s="11">
-        <v>2405</v>
+        <v>2148</v>
       </c>
       <c r="E132" s="11">
         <v>0</v>
       </c>
       <c r="F132" s="11">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="G132" s="11">
-        <f t="shared" ref="G132:G146" si="4">SUM(B132:F132)</f>
-        <v>2505</v>
+        <f t="shared" si="4"/>
+        <v>2203</v>
       </c>
       <c r="H132" s="11">
         <v>0</v>
       </c>
       <c r="I132" s="5"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9">
       <c r="A133" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B133" s="11">
         <v>0</v>
       </c>
       <c r="C133" s="11"/>
       <c r="D133" s="11">
-        <v>275</v>
+        <v>4055</v>
       </c>
       <c r="E133" s="11">
         <v>0</v>
       </c>
       <c r="F133" s="11">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="G133" s="11">
         <f t="shared" si="4"/>
-        <v>330</v>
+        <v>4185</v>
       </c>
       <c r="H133" s="11">
         <v>0</v>
       </c>
       <c r="I133" s="5"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9">
       <c r="A134" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B134" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C134" s="11"/>
       <c r="D134" s="11">
-        <v>2115</v>
+        <v>0</v>
       </c>
       <c r="E134" s="11">
         <v>0</v>
       </c>
       <c r="F134" s="11">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="G134" s="11">
         <f t="shared" si="4"/>
-        <v>2245</v>
+        <v>2</v>
       </c>
       <c r="H134" s="11">
         <v>0</v>
       </c>
       <c r="I134" s="5"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9">
       <c r="A135" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B135" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C135" s="11"/>
       <c r="D135" s="11">
@@ -5046,16 +5472,16 @@
       </c>
       <c r="G135" s="11">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135" s="11">
         <v>0</v>
       </c>
       <c r="I135" s="5"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9">
       <c r="A136" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B136" s="11">
         <v>0</v>
@@ -5079,9 +5505,9 @@
       </c>
       <c r="I136" s="5"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9">
       <c r="A137" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B137" s="11">
         <v>0</v>
@@ -5094,20 +5520,20 @@
         <v>0</v>
       </c>
       <c r="F137" s="11">
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="G137" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="H137" s="11">
         <v>0</v>
       </c>
       <c r="I137" s="5"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9">
       <c r="A138" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B138" s="11">
         <v>0</v>
@@ -5120,23 +5546,23 @@
         <v>0</v>
       </c>
       <c r="F138" s="11">
-        <v>442</v>
+        <v>258</v>
       </c>
       <c r="G138" s="11">
         <f t="shared" si="4"/>
-        <v>442</v>
+        <v>258</v>
       </c>
       <c r="H138" s="11">
         <v>0</v>
       </c>
       <c r="I138" s="5"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9">
       <c r="A139" s="10" t="s">
-        <v>54</v>
+        <v>243</v>
       </c>
       <c r="B139" s="11">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C139" s="11"/>
       <c r="D139" s="11">
@@ -5146,23 +5572,23 @@
         <v>0</v>
       </c>
       <c r="F139" s="11">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="G139" s="11">
         <f t="shared" si="4"/>
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="H139" s="11">
         <v>0</v>
       </c>
       <c r="I139" s="5"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9">
       <c r="A140" s="10" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B140" s="11">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="C140" s="11"/>
       <c r="D140" s="11">
@@ -5176,19 +5602,19 @@
       </c>
       <c r="G140" s="11">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="H140" s="11">
         <v>0</v>
       </c>
       <c r="I140" s="5"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9">
       <c r="A141" s="10" t="s">
-        <v>241</v>
+        <v>68</v>
       </c>
       <c r="B141" s="11">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C141" s="11"/>
       <c r="D141" s="11">
@@ -5202,19 +5628,19 @@
       </c>
       <c r="G141" s="11">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H141" s="11">
         <v>0</v>
       </c>
       <c r="I141" s="5"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9">
       <c r="A142" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B142" s="11">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C142" s="11"/>
       <c r="D142" s="11">
@@ -5228,45 +5654,45 @@
       </c>
       <c r="G142" s="11">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H142" s="11">
         <v>0</v>
       </c>
       <c r="I142" s="5"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9">
       <c r="A143" s="10" t="s">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="B143" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C143" s="11"/>
       <c r="D143" s="11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E143" s="11">
         <v>0</v>
       </c>
       <c r="F143" s="11">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="G143" s="11">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>42.13</v>
       </c>
       <c r="H143" s="11">
         <v>0</v>
       </c>
       <c r="I143" s="5"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9">
       <c r="A144" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B144" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144" s="11"/>
       <c r="D144" s="11">
@@ -5280,19 +5706,19 @@
       </c>
       <c r="G144" s="11">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H144" s="11">
         <v>0</v>
       </c>
       <c r="I144" s="5"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9">
       <c r="A145" s="10" t="s">
-        <v>73</v>
+        <v>238</v>
       </c>
       <c r="B145" s="11">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C145" s="11"/>
       <c r="D145" s="11">
@@ -5306,19 +5732,19 @@
       </c>
       <c r="G145" s="11">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H145" s="11">
         <v>0</v>
       </c>
       <c r="I145" s="5"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9">
       <c r="A146" s="10" t="s">
-        <v>242</v>
+        <v>56</v>
       </c>
       <c r="B146" s="11">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="C146" s="11"/>
       <c r="D146" s="11">
@@ -5331,20 +5757,19 @@
         <v>0</v>
       </c>
       <c r="G146" s="11">
-        <f t="shared" si="4"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H146" s="11">
         <v>0</v>
       </c>
       <c r="I146" s="5"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9">
       <c r="A147" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B147" s="11">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="C147" s="11"/>
       <c r="D147" s="11">
@@ -5364,9 +5789,9 @@
       </c>
       <c r="I147" s="5"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9">
       <c r="A148" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B148" s="11">
         <v>0</v>
@@ -5389,12 +5814,12 @@
       </c>
       <c r="I148" s="5"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9">
       <c r="A149" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B149" s="11">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="C149" s="11"/>
       <c r="D149" s="11">
@@ -5414,43 +5839,43 @@
       </c>
       <c r="I149" s="5"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9">
       <c r="A150" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B150" s="11">
-        <v>6.5</v>
-      </c>
-      <c r="C150" s="11"/>
+        <v>0</v>
+      </c>
+      <c r="C150" s="13"/>
       <c r="D150" s="11">
         <v>0</v>
       </c>
       <c r="E150" s="11">
         <v>0</v>
       </c>
-      <c r="F150" s="11">
-        <v>0</v>
-      </c>
-      <c r="G150" s="11">
-        <v>0</v>
-      </c>
-      <c r="H150" s="11">
-        <v>0</v>
-      </c>
-      <c r="I150" s="5"/>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F150" s="13">
+        <v>0</v>
+      </c>
+      <c r="G150" s="13">
+        <v>0</v>
+      </c>
+      <c r="H150" s="13">
+        <v>0</v>
+      </c>
+      <c r="I150" s="7"/>
+    </row>
+    <row r="151" spans="1:9">
       <c r="A151" s="10" t="s">
-        <v>69</v>
+        <v>242</v>
       </c>
       <c r="B151" s="11">
         <v>0</v>
       </c>
       <c r="C151" s="13"/>
-      <c r="D151" s="13">
-        <v>0</v>
-      </c>
-      <c r="E151" s="13">
+      <c r="D151" s="11">
+        <v>0</v>
+      </c>
+      <c r="E151" s="11">
         <v>0</v>
       </c>
       <c r="F151" s="13">
@@ -5464,58 +5889,34 @@
       </c>
       <c r="I151" s="7"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A152" s="10" t="s">
+    <row r="152" spans="1:9" ht="19.5" thickBot="1">
+      <c r="A152" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="B152" s="11">
-        <v>0</v>
-      </c>
-      <c r="C152" s="13"/>
-      <c r="D152" s="13">
-        <v>0</v>
-      </c>
-      <c r="E152" s="13">
-        <v>0</v>
-      </c>
-      <c r="F152" s="13">
-        <v>0</v>
-      </c>
-      <c r="G152" s="13">
-        <v>0</v>
-      </c>
-      <c r="H152" s="13">
-        <v>0</v>
-      </c>
-      <c r="I152" s="7"/>
-    </row>
-    <row r="153" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="B153" s="14">
+      <c r="B152" s="14">
         <v>7</v>
       </c>
-      <c r="C153" s="15"/>
-      <c r="D153" s="15">
-        <v>0</v>
-      </c>
-      <c r="E153" s="15">
-        <v>0</v>
-      </c>
-      <c r="F153" s="15">
-        <v>0</v>
-      </c>
-      <c r="G153" s="15">
-        <v>0</v>
-      </c>
-      <c r="H153" s="15">
-        <v>0</v>
-      </c>
-      <c r="I153" s="8"/>
+      <c r="C152" s="15"/>
+      <c r="D152" s="14">
+        <v>0</v>
+      </c>
+      <c r="E152" s="14">
+        <v>0</v>
+      </c>
+      <c r="F152" s="15">
+        <v>0</v>
+      </c>
+      <c r="G152" s="15">
+        <v>0</v>
+      </c>
+      <c r="H152" s="15">
+        <v>0</v>
+      </c>
+      <c r="I152" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H375" xr:uid="{69590074-F9E1-47CB-9D65-9D1D53B05140}"/>
+  <sheetProtection autoFilter="0"/>
+  <autoFilter ref="A4:H374" xr:uid="{69590074-F9E1-47CB-9D65-9D1D53B05140}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
